--- a/MU DCF.xlsx
+++ b/MU DCF.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wccedu-my.sharepoint.com/personal/joheim_wccnet_edu/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonahheim/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="774" documentId="8_{F4ED0B03-FAC3-174D-824D-A3BC60038D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0A14EDC-A80C-C647-A4F7-381F58F16B20}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D992A4-1C58-9547-A0F7-BF6F11EB729F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40900" yWindow="0" windowWidth="26900" windowHeight="21600" activeTab="1" xr2:uid="{2ED523F7-DD53-F241-828A-87AFBE2FEF6A}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17260" activeTab="2" xr2:uid="{2ED523F7-DD53-F241-828A-87AFBE2FEF6A}"/>
   </bookViews>
   <sheets>
     <sheet name="DCF" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <definedName name="tgr">[1]DCF!$E$19</definedName>
     <definedName name="wacc">[1]DCF!$E$18</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1228,7 +1228,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1281,8 +1281,6 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1295,9 +1293,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="4"/>
-    </xf>
     <xf numFmtId="10" fontId="9" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1333,7 +1328,6 @@
     <xf numFmtId="14" fontId="17" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="17" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1348,28 +1342,21 @@
     <xf numFmtId="9" fontId="17" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="17" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="17" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="17" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="17" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="41" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="20" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="17" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="17" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="17" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="19" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="17" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="17" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="43" fontId="17" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1377,12 +1364,9 @@
     <xf numFmtId="10" fontId="17" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="17" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="17" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="17" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="17" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="17" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1494,17 +1478,15 @@
 
 <file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
 <arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="2">
-  <a r="1" c="4">
+  <a r="1" c="3">
     <v t="i">0</v>
     <v t="i">1</v>
-    <v t="i">3</v>
-    <v t="i">6</v>
+    <v t="i">2</v>
   </a>
-  <a r="1" c="4">
-    <v>276.27</v>
-    <v>286.68</v>
-    <v>284.79000000000002</v>
-    <v>294.37</v>
+  <a r="1" c="3">
+    <v>956.08</v>
+    <v>958.16</v>
+    <v>1016.59</v>
   </a>
 </arrayData>
 </file>
@@ -1512,18 +1494,18 @@
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
 <rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
   <rv s="0">
-    <fb>294.37</fb>
+    <fb>1016.59</fb>
     <v>0</v>
   </rv>
   <rv s="1">
     <v>1</v>
     <v>MU</v>
     <v>Daily</v>
-    <v>46014</v>
-    <v>46020</v>
+    <v>46267</v>
+    <v>46273</v>
     <v>0</v>
     <v>1</v>
-    <v>639025632000000000,639027006032172057,0</v>
+    <v>639240768000000000,639245641448787368,0</v>
     <v>0</v>
     <v>a1y4oc</v>
     <v>XNAS:MU</v>
@@ -1919,110 +1901,109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF70CAC8-3A6D-1B4D-B90A-4C1C007DB222}">
-  <dimension ref="A2:N101"/>
+  <dimension ref="A2:N74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" style="51" customWidth="1"/>
-    <col min="2" max="2" width="24.33203125" style="51" customWidth="1"/>
-    <col min="3" max="13" width="14.83203125" style="51" customWidth="1"/>
-    <col min="14" max="14" width="2.83203125" style="51" customWidth="1"/>
-    <col min="15" max="15" width="14.83203125" style="51" customWidth="1"/>
-    <col min="16" max="16384" width="10.83203125" style="51"/>
+    <col min="1" max="1" width="2.83203125" style="48" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" style="48" customWidth="1"/>
+    <col min="3" max="13" width="14.83203125" style="48" customWidth="1"/>
+    <col min="14" max="14" width="2.83203125" style="48" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" style="48" customWidth="1"/>
+    <col min="16" max="16384" width="10.83203125" style="48"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" s="50" customFormat="1" ht="22" x14ac:dyDescent="0.3">
-      <c r="B2" s="106" t="s">
+    <row r="2" spans="1:14" s="47" customFormat="1" ht="22" x14ac:dyDescent="0.3">
+      <c r="B2" s="92" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F3" s="52"/>
+      <c r="F3" s="49"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="48" t="s">
         <v>139</v>
       </c>
-      <c r="F4" s="54"/>
-      <c r="G4" s="55">
+      <c r="F4" s="51"/>
+      <c r="G4" s="52">
         <f ca="1">C73</f>
-        <v>390.14579183226857</v>
+        <v>378.69878657924386</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="48" t="s">
         <v>127</v>
       </c>
-      <c r="C5" s="56">
+      <c r="C5" s="53">
         <f>WACC!F11</f>
         <v>1122.4666035</v>
       </c>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="F5" s="57"/>
-      <c r="G5" s="58">
+      <c r="F5" s="54"/>
+      <c r="G5" s="55">
         <f ca="1">(G4/C6)-1</f>
-        <v>0.32535853460702024</v>
+        <v>-0.62748129867572588</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="48" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="59" vm="1">
+      <c r="C6" s="56" vm="1">
         <f ca="1">WACC!F10</f>
-        <v>294.37</v>
-      </c>
-      <c r="F6" s="52"/>
+        <v>1016.59</v>
+      </c>
+      <c r="F6" s="49"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="C7" s="60">
+      <c r="C7" s="57">
         <f ca="1">C6*C5</f>
-        <v>330420.49407229503</v>
-      </c>
-      <c r="E7" s="51" t="s">
+        <v>1141088.3244520652</v>
+      </c>
+      <c r="E7" s="48" t="s">
         <v>134</v>
       </c>
-      <c r="F7" s="54"/>
-      <c r="G7" s="55">
+      <c r="F7" s="51"/>
+      <c r="G7" s="52">
         <f ca="1">C71</f>
-        <v>442970.62182778458</v>
+        <v>430121.74072117521</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="61">
+      <c r="C8" s="58">
         <v>46020</v>
       </c>
-      <c r="E8" s="51" t="s">
+      <c r="E8" s="48" t="s">
         <v>135</v>
       </c>
-      <c r="F8" s="54"/>
-      <c r="G8" s="55">
+      <c r="F8" s="51"/>
+      <c r="G8" s="52">
         <f ca="1">C72</f>
-        <v>437925.62182778458</v>
+        <v>425076.74072117521</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="61">
+      <c r="C9" s="58">
         <v>46022</v>
       </c>
-      <c r="F9" s="52"/>
-      <c r="G9" s="62"/>
+      <c r="F9" s="49"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
@@ -2031,2182 +2012,1955 @@
     </row>
     <row r="12" spans="1:14" ht="5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="63">
+      <c r="C13" s="59">
         <f ca="1">WACC!F27</f>
-        <v>0.11496683908739169</v>
+        <v>0.11752771487876082</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="63">
+      <c r="C14" s="59">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="105"/>
-      <c r="B16" s="64" t="s">
+      <c r="A16" s="91"/>
+      <c r="B16" s="60" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="65" t="s">
+      <c r="C16" s="61" t="s">
         <v>111</v>
       </c>
-      <c r="D16" s="65" t="s">
+      <c r="D16" s="61" t="s">
         <v>112</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="61" t="s">
         <v>109</v>
       </c>
-      <c r="F16" s="65" t="s">
+      <c r="F16" s="61" t="s">
         <v>110</v>
       </c>
-      <c r="G16" s="65" t="s">
+      <c r="G16" s="61" t="s">
         <v>113</v>
       </c>
-      <c r="H16" s="65" t="s">
+      <c r="H16" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="I16" s="65" t="s">
+      <c r="I16" s="61" t="s">
         <v>115</v>
       </c>
-      <c r="J16" s="65" t="s">
+      <c r="J16" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="K16" s="65" t="s">
+      <c r="K16" s="61" t="s">
         <v>117</v>
       </c>
-      <c r="L16" s="65" t="s">
+      <c r="L16" s="61" t="s">
         <v>118</v>
       </c>
-      <c r="M16" s="65" t="s">
+      <c r="M16" s="61" t="s">
         <v>119</v>
       </c>
-      <c r="N16" s="105"/>
+      <c r="N16" s="91"/>
     </row>
     <row r="17" spans="1:14" ht="5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="100"/>
-      <c r="B18" s="101" t="s">
+      <c r="A18" s="87"/>
+      <c r="B18" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="C18" s="100"/>
-      <c r="D18" s="100"/>
-      <c r="E18" s="100"/>
-      <c r="F18" s="100"/>
-      <c r="G18" s="100"/>
-      <c r="H18" s="100"/>
-      <c r="I18" s="100"/>
-      <c r="J18" s="100"/>
-      <c r="K18" s="100"/>
-      <c r="L18" s="100"/>
-      <c r="M18" s="100"/>
-      <c r="N18" s="100"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="87"/>
+      <c r="I18" s="87"/>
+      <c r="J18" s="87"/>
+      <c r="K18" s="87"/>
+      <c r="L18" s="87"/>
+      <c r="M18" s="87"/>
+      <c r="N18" s="87"/>
     </row>
     <row r="19" spans="1:14" ht="5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="100"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="62"/>
-      <c r="M19" s="62"/>
-      <c r="N19" s="100"/>
+      <c r="A19" s="87"/>
+      <c r="G19" s="62"/>
+      <c r="N19" s="87"/>
     </row>
     <row r="20" spans="1:14" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="100"/>
-      <c r="B20" s="51" t="s">
+      <c r="A20" s="87"/>
+      <c r="B20" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="67">
+      <c r="C20" s="63">
         <f>'Income Statement'!F5</f>
         <v>30758</v>
       </c>
-      <c r="D20" s="68">
+      <c r="D20" s="64">
         <f>'Income Statement'!G5</f>
         <v>15540</v>
       </c>
-      <c r="E20" s="68">
+      <c r="E20" s="64">
         <f>'Income Statement'!H5</f>
         <v>25111</v>
       </c>
-      <c r="F20" s="68">
+      <c r="F20" s="64">
         <f>'Income Statement'!I5</f>
         <v>37378</v>
       </c>
-      <c r="G20" s="69">
+      <c r="G20" s="65">
         <f>F20*(1+G21)</f>
         <v>73810.336599999995</v>
       </c>
-      <c r="H20" s="70">
+      <c r="H20" s="66">
         <f t="shared" ref="H20:M20" si="0">G20*(1+H21)</f>
         <v>90786.714017999999</v>
       </c>
-      <c r="I20" s="70">
+      <c r="I20" s="66">
         <f t="shared" si="0"/>
         <v>106220.45540106</v>
       </c>
-      <c r="J20" s="70">
+      <c r="J20" s="66">
         <f t="shared" si="0"/>
         <v>118966.91004918721</v>
       </c>
-      <c r="K20" s="70">
+      <c r="K20" s="66">
         <f t="shared" si="0"/>
         <v>128484.2628531222</v>
       </c>
-      <c r="L20" s="70">
+      <c r="L20" s="66">
         <f t="shared" si="0"/>
         <v>135165.44452148455</v>
       </c>
-      <c r="M20" s="70">
+      <c r="M20" s="66">
         <f t="shared" si="0"/>
         <v>142194.04763660175</v>
       </c>
-      <c r="N20" s="100"/>
+      <c r="N20" s="87"/>
     </row>
     <row r="21" spans="1:14" ht="20" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="100"/>
-      <c r="B21" s="51" t="s">
+      <c r="A21" s="87"/>
+      <c r="B21" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="94">
+      <c r="C21" s="83">
         <f>(C20-'Income Statement'!E5)/'Income Statement'!E5</f>
         <v>0.11019671539433315</v>
       </c>
-      <c r="D21" s="95">
+      <c r="D21" s="84">
         <f t="shared" ref="D21" si="1">(D20-C20)/C20</f>
         <v>-0.49476558944014565</v>
       </c>
-      <c r="E21" s="95">
+      <c r="E21" s="84">
         <f>(E20-D20)/D20</f>
         <v>0.61589446589446595</v>
       </c>
-      <c r="F21" s="95">
+      <c r="F21" s="84">
         <f t="shared" ref="F21" si="2">(F20-E20)/E20</f>
         <v>0.48851101111066864</v>
       </c>
-      <c r="G21" s="96">
+      <c r="G21" s="85">
         <v>0.97470000000000001</v>
       </c>
-      <c r="H21" s="97">
+      <c r="H21" s="86">
         <v>0.23</v>
       </c>
-      <c r="I21" s="97">
+      <c r="I21" s="86">
         <v>0.17</v>
       </c>
-      <c r="J21" s="97">
+      <c r="J21" s="86">
         <v>0.12</v>
       </c>
-      <c r="K21" s="97">
+      <c r="K21" s="86">
         <v>0.08</v>
       </c>
-      <c r="L21" s="97">
+      <c r="L21" s="86">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="M21" s="97">
+      <c r="M21" s="86">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="N21" s="100"/>
+      <c r="N21" s="87"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="100"/>
-      <c r="C22" s="71"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="75"/>
-      <c r="J22" s="75"/>
-      <c r="K22" s="75"/>
-      <c r="L22" s="75"/>
-      <c r="M22" s="75"/>
-      <c r="N22" s="100"/>
+      <c r="A22" s="87"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="67"/>
+      <c r="N22" s="87"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="100"/>
-      <c r="B23" s="51" t="s">
+      <c r="A23" s="87"/>
+      <c r="B23" s="48" t="s">
         <v>120</v>
       </c>
-      <c r="C23" s="68">
+      <c r="C23" s="64">
         <f>'Income Statement'!F7</f>
         <v>9744</v>
       </c>
-      <c r="D23" s="68">
+      <c r="D23" s="64">
         <f>'Income Statement'!G7</f>
         <v>9200</v>
       </c>
-      <c r="E23" s="68">
+      <c r="E23" s="64">
         <f>'Income Statement'!H7</f>
         <v>11718</v>
       </c>
-      <c r="F23" s="68">
+      <c r="F23" s="64">
         <f>'Income Statement'!I7</f>
         <v>14153</v>
       </c>
-      <c r="G23" s="76">
+      <c r="G23" s="71">
         <f>G20*G25</f>
         <v>22143.100979999999</v>
       </c>
-      <c r="H23" s="77">
+      <c r="H23" s="72">
         <f t="shared" ref="H23:M23" si="3">H20*H25</f>
         <v>29051.748485759999</v>
       </c>
-      <c r="I23" s="77">
+      <c r="I23" s="72">
         <f t="shared" si="3"/>
         <v>37177.159390370995</v>
       </c>
-      <c r="J23" s="77">
+      <c r="J23" s="72">
         <f t="shared" si="3"/>
         <v>38069.411215739907</v>
       </c>
-      <c r="K23" s="77">
+      <c r="K23" s="72">
         <f t="shared" si="3"/>
         <v>35975.59359887422</v>
       </c>
-      <c r="L23" s="77">
+      <c r="L23" s="72">
         <f t="shared" si="3"/>
         <v>37846.324466015678</v>
       </c>
-      <c r="M23" s="77">
+      <c r="M23" s="72">
         <f t="shared" si="3"/>
         <v>39814.333338248493</v>
       </c>
-      <c r="N23" s="100"/>
+      <c r="N23" s="87"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="100"/>
-      <c r="B24" s="51" t="s">
+      <c r="A24" s="87"/>
+      <c r="B24" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="72">
+      <c r="C24" s="68">
         <f>(C23-'Income Statement'!E7)/'Income Statement'!E7</f>
         <v>-0.11962414166967836</v>
       </c>
-      <c r="D24" s="72">
+      <c r="D24" s="68">
         <f t="shared" ref="D24:M24" si="4">(D23-C23)/C23</f>
         <v>-5.5829228243021348E-2</v>
       </c>
-      <c r="E24" s="72">
+      <c r="E24" s="68">
         <f t="shared" si="4"/>
         <v>0.27369565217391306</v>
       </c>
-      <c r="F24" s="72">
+      <c r="F24" s="68">
         <f t="shared" si="4"/>
         <v>0.20779996586448199</v>
       </c>
-      <c r="G24" s="78">
+      <c r="G24" s="73">
         <f t="shared" si="4"/>
         <v>0.56455175439836069</v>
       </c>
-      <c r="H24" s="73">
+      <c r="H24" s="69">
         <f t="shared" si="4"/>
         <v>0.312</v>
       </c>
-      <c r="I24" s="73">
+      <c r="I24" s="69">
         <f>(I23-H23)/H23</f>
         <v>0.27968749999999987</v>
       </c>
-      <c r="J24" s="73">
+      <c r="J24" s="69">
         <f t="shared" si="4"/>
         <v>2.4000000000000226E-2</v>
       </c>
-      <c r="K24" s="73">
+      <c r="K24" s="69">
         <f t="shared" si="4"/>
         <v>-5.4999999999999778E-2</v>
       </c>
-      <c r="L24" s="73">
+      <c r="L24" s="69">
         <f t="shared" si="4"/>
         <v>5.1999999999999949E-2</v>
       </c>
-      <c r="M24" s="73">
+      <c r="M24" s="69">
         <f t="shared" si="4"/>
         <v>5.1999999999999984E-2</v>
       </c>
-      <c r="N24" s="100"/>
+      <c r="N24" s="87"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="100"/>
-      <c r="B25" s="51" t="s">
+      <c r="A25" s="87"/>
+      <c r="B25" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="71">
+      <c r="C25" s="67">
         <f>C23/C20</f>
         <v>0.31679563040509784</v>
       </c>
-      <c r="D25" s="71">
+      <c r="D25" s="67">
         <f>D23/D20</f>
         <v>0.59202059202059198</v>
       </c>
-      <c r="E25" s="71">
+      <c r="E25" s="67">
         <f>E23/E20</f>
         <v>0.46664808251363943</v>
       </c>
-      <c r="F25" s="71">
+      <c r="F25" s="67">
         <f>F23/F20</f>
         <v>0.37864519235914174</v>
       </c>
-      <c r="G25" s="74">
+      <c r="G25" s="70">
         <v>0.3</v>
       </c>
-      <c r="H25" s="75">
+      <c r="H25" s="67">
         <v>0.32</v>
       </c>
-      <c r="I25" s="75">
+      <c r="I25" s="67">
         <v>0.35</v>
       </c>
-      <c r="J25" s="75">
+      <c r="J25" s="67">
         <v>0.32</v>
       </c>
-      <c r="K25" s="75">
+      <c r="K25" s="67">
         <v>0.28000000000000003</v>
       </c>
-      <c r="L25" s="75">
+      <c r="L25" s="67">
         <v>0.28000000000000003</v>
       </c>
-      <c r="M25" s="75">
+      <c r="M25" s="67">
         <v>0.28000000000000003</v>
       </c>
-      <c r="N25" s="100"/>
+      <c r="N25" s="87"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="100"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="71"/>
-      <c r="E26" s="71"/>
-      <c r="F26" s="71"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="75"/>
-      <c r="I26" s="75"/>
-      <c r="J26" s="75"/>
-      <c r="K26" s="75"/>
-      <c r="L26" s="75"/>
-      <c r="M26" s="75"/>
-      <c r="N26" s="100"/>
+      <c r="A26" s="87"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="67"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="67"/>
+      <c r="I26" s="67"/>
+      <c r="J26" s="67"/>
+      <c r="K26" s="67"/>
+      <c r="L26" s="67"/>
+      <c r="M26" s="67"/>
+      <c r="N26" s="87"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="100"/>
-      <c r="B27" s="51" t="s">
+      <c r="A27" s="87"/>
+      <c r="B27" s="48" t="s">
         <v>141</v>
       </c>
-      <c r="C27" s="82">
+      <c r="C27" s="72">
         <f>C20-C23</f>
         <v>21014</v>
       </c>
-      <c r="D27" s="82">
+      <c r="D27" s="72">
         <f t="shared" ref="D27:M27" si="5">D20-D23</f>
         <v>6340</v>
       </c>
-      <c r="E27" s="82">
+      <c r="E27" s="72">
         <f t="shared" si="5"/>
         <v>13393</v>
       </c>
-      <c r="F27" s="82">
+      <c r="F27" s="72">
         <f t="shared" si="5"/>
         <v>23225</v>
       </c>
-      <c r="G27" s="76">
+      <c r="G27" s="71">
         <f t="shared" si="5"/>
         <v>51667.235619999992</v>
       </c>
-      <c r="H27" s="82">
+      <c r="H27" s="72">
         <f t="shared" si="5"/>
         <v>61734.965532239999</v>
       </c>
-      <c r="I27" s="82">
+      <c r="I27" s="72">
         <f t="shared" si="5"/>
         <v>69043.296010688995</v>
       </c>
-      <c r="J27" s="82">
+      <c r="J27" s="72">
         <f t="shared" si="5"/>
         <v>80897.498833447302</v>
       </c>
-      <c r="K27" s="82">
+      <c r="K27" s="72">
         <f t="shared" si="5"/>
         <v>92508.669254247972</v>
       </c>
-      <c r="L27" s="82">
+      <c r="L27" s="72">
         <f t="shared" si="5"/>
         <v>97319.120055468869</v>
       </c>
-      <c r="M27" s="82">
+      <c r="M27" s="72">
         <f t="shared" si="5"/>
         <v>102379.71429835327</v>
       </c>
-      <c r="N27" s="100"/>
+      <c r="N27" s="87"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="100"/>
-      <c r="B28" s="51" t="s">
+      <c r="A28" s="87"/>
+      <c r="B28" s="48" t="s">
         <v>142</v>
       </c>
-      <c r="C28" s="71">
+      <c r="C28" s="67">
         <f>C27/C20</f>
         <v>0.68320436959490216</v>
       </c>
-      <c r="D28" s="71">
+      <c r="D28" s="67">
         <f t="shared" ref="D28:M28" si="6">D27/D20</f>
         <v>0.40797940797940796</v>
       </c>
-      <c r="E28" s="71">
+      <c r="E28" s="67">
         <f t="shared" si="6"/>
         <v>0.53335191748636057</v>
       </c>
-      <c r="F28" s="71">
+      <c r="F28" s="67">
         <f t="shared" si="6"/>
         <v>0.62135480764085826</v>
       </c>
-      <c r="G28" s="74">
+      <c r="G28" s="70">
         <f t="shared" si="6"/>
         <v>0.7</v>
       </c>
-      <c r="H28" s="71">
+      <c r="H28" s="67">
         <f t="shared" si="6"/>
         <v>0.68</v>
       </c>
-      <c r="I28" s="71">
+      <c r="I28" s="67">
         <f t="shared" si="6"/>
         <v>0.65</v>
       </c>
-      <c r="J28" s="71">
+      <c r="J28" s="67">
         <f t="shared" si="6"/>
         <v>0.68</v>
       </c>
-      <c r="K28" s="71">
+      <c r="K28" s="67">
         <f t="shared" si="6"/>
         <v>0.71999999999999986</v>
       </c>
-      <c r="L28" s="71">
+      <c r="L28" s="67">
         <f t="shared" si="6"/>
         <v>0.72</v>
       </c>
-      <c r="M28" s="71">
+      <c r="M28" s="67">
         <f t="shared" si="6"/>
         <v>0.72000000000000008</v>
       </c>
-      <c r="N28" s="100"/>
+      <c r="N28" s="87"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="100"/>
-      <c r="C29" s="71"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="71"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="74"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="71"/>
-      <c r="K29" s="71"/>
-      <c r="L29" s="71"/>
-      <c r="M29" s="71"/>
-      <c r="N29" s="100"/>
+      <c r="A29" s="87"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="67"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="67"/>
+      <c r="J29" s="67"/>
+      <c r="K29" s="67"/>
+      <c r="L29" s="67"/>
+      <c r="M29" s="67"/>
+      <c r="N29" s="87"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="100"/>
-      <c r="B30" s="51" t="s">
+      <c r="A30" s="87"/>
+      <c r="B30" s="48" t="s">
         <v>143</v>
       </c>
-      <c r="C30" s="82">
+      <c r="C30" s="72">
         <f>SUM('Income Statement'!F10:F12)</f>
         <v>4148</v>
       </c>
-      <c r="D30" s="82">
+      <c r="D30" s="72">
         <f>SUM('Income Statement'!G10:G12)</f>
         <v>4158</v>
       </c>
-      <c r="E30" s="82">
+      <c r="E30" s="72">
         <f>SUM('Income Statement'!H10:H12)</f>
         <v>4308</v>
       </c>
-      <c r="F30" s="82">
+      <c r="F30" s="72">
         <f>SUM('Income Statement'!I10:I12)</f>
         <v>5064</v>
       </c>
-      <c r="G30" s="76">
+      <c r="G30" s="71">
         <v>5900</v>
       </c>
-      <c r="H30" s="98">
+      <c r="H30" s="75">
         <f>H20*H31</f>
         <v>9078.6714018000002</v>
       </c>
-      <c r="I30" s="98">
+      <c r="I30" s="75">
         <f t="shared" ref="I30:M30" si="7">I20*I31</f>
         <v>10622.045540106001</v>
       </c>
-      <c r="J30" s="98">
+      <c r="J30" s="75">
         <f t="shared" si="7"/>
         <v>11896.691004918721</v>
       </c>
-      <c r="K30" s="98">
+      <c r="K30" s="75">
         <f t="shared" si="7"/>
         <v>12848.42628531222</v>
       </c>
-      <c r="L30" s="98">
+      <c r="L30" s="75">
         <f t="shared" si="7"/>
         <v>13516.544452148455</v>
       </c>
-      <c r="M30" s="98">
+      <c r="M30" s="75">
         <f t="shared" si="7"/>
         <v>14219.404763660175</v>
       </c>
-      <c r="N30" s="100"/>
+      <c r="N30" s="87"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="100"/>
-      <c r="B31" s="51" t="s">
+      <c r="A31" s="87"/>
+      <c r="B31" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="C31" s="71">
+      <c r="C31" s="67">
         <f>C30/C20</f>
         <v>0.13485922361662006</v>
       </c>
-      <c r="D31" s="71">
+      <c r="D31" s="67">
         <f t="shared" ref="D31:G31" si="8">D30/D20</f>
         <v>0.26756756756756755</v>
       </c>
-      <c r="E31" s="71">
+      <c r="E31" s="67">
         <f t="shared" si="8"/>
         <v>0.17155828123133288</v>
       </c>
-      <c r="F31" s="71">
+      <c r="F31" s="67">
         <f t="shared" si="8"/>
         <v>0.13548076408582588</v>
       </c>
-      <c r="G31" s="74">
+      <c r="G31" s="70">
         <f t="shared" si="8"/>
         <v>7.9934603631112558E-2</v>
       </c>
-      <c r="H31" s="75">
+      <c r="H31" s="67">
         <v>0.1</v>
       </c>
-      <c r="I31" s="75">
+      <c r="I31" s="67">
         <v>0.1</v>
       </c>
-      <c r="J31" s="75">
+      <c r="J31" s="67">
         <v>0.1</v>
       </c>
-      <c r="K31" s="75">
+      <c r="K31" s="67">
         <v>0.1</v>
       </c>
-      <c r="L31" s="75">
+      <c r="L31" s="67">
         <v>0.1</v>
       </c>
-      <c r="M31" s="75">
+      <c r="M31" s="67">
         <v>0.1</v>
       </c>
-      <c r="N31" s="100"/>
+      <c r="N31" s="87"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="100"/>
-      <c r="G32" s="66"/>
-      <c r="H32" s="62"/>
-      <c r="I32" s="62"/>
-      <c r="J32" s="62"/>
-      <c r="K32" s="62"/>
-      <c r="L32" s="62"/>
-      <c r="M32" s="62"/>
-      <c r="N32" s="100"/>
+      <c r="A32" s="87"/>
+      <c r="G32" s="62"/>
+      <c r="N32" s="87"/>
     </row>
     <row r="33" spans="1:14" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="100"/>
-      <c r="B33" s="51" t="s">
+      <c r="A33" s="87"/>
+      <c r="B33" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="68">
+      <c r="C33" s="64">
         <f>'Income Statement'!F13</f>
         <v>9702</v>
       </c>
-      <c r="D33" s="68">
+      <c r="D33" s="64">
         <f>'Income Statement'!G13</f>
         <v>-5745</v>
       </c>
-      <c r="E33" s="68">
+      <c r="E33" s="64">
         <f>'Income Statement'!H13</f>
         <v>1304</v>
       </c>
-      <c r="F33" s="68">
+      <c r="F33" s="64">
         <f>'Income Statement'!I13</f>
         <v>9770</v>
       </c>
-      <c r="G33" s="69">
+      <c r="G33" s="65">
         <f>G20-G23-G30</f>
         <v>45767.235619999992</v>
       </c>
-      <c r="H33" s="70">
+      <c r="H33" s="66">
         <f t="shared" ref="H33:M33" si="9">H20-H23-H30</f>
         <v>52656.294130440001</v>
       </c>
-      <c r="I33" s="70">
+      <c r="I33" s="66">
         <f t="shared" si="9"/>
         <v>58421.250470582992</v>
       </c>
-      <c r="J33" s="70">
+      <c r="J33" s="66">
         <f t="shared" si="9"/>
         <v>69000.807828528574</v>
       </c>
-      <c r="K33" s="70">
+      <c r="K33" s="66">
         <f t="shared" si="9"/>
         <v>79660.242968935752</v>
       </c>
-      <c r="L33" s="70">
+      <c r="L33" s="66">
         <f t="shared" si="9"/>
         <v>83802.575603320409</v>
       </c>
-      <c r="M33" s="70">
+      <c r="M33" s="66">
         <f t="shared" si="9"/>
         <v>88160.309534693093</v>
       </c>
-      <c r="N33" s="100"/>
+      <c r="N33" s="87"/>
     </row>
     <row r="34" spans="1:14" ht="20" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="100"/>
-      <c r="B34" s="51" t="s">
+      <c r="A34" s="87"/>
+      <c r="B34" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="72">
+      <c r="C34" s="68">
         <f>(C33-'Income Statement'!E13)/'Income Statement'!E13</f>
         <v>0.54416679929969758</v>
       </c>
-      <c r="D34" s="72">
+      <c r="D34" s="68">
         <f t="shared" ref="D34" si="10">(D33-C33)/C33</f>
         <v>-1.5921459492888064</v>
       </c>
-      <c r="E34" s="72">
+      <c r="E34" s="68">
         <f t="shared" ref="E34" si="11">(E33-D33)/D33</f>
         <v>-1.2269799825935597</v>
       </c>
-      <c r="F34" s="72">
+      <c r="F34" s="68">
         <f t="shared" ref="F34" si="12">(F33-E33)/E33</f>
         <v>6.492331288343558</v>
       </c>
-      <c r="G34" s="78">
+      <c r="G34" s="73">
         <f t="shared" ref="G34" si="13">(G33-F33)/F33</f>
         <v>3.684466286591606</v>
       </c>
-      <c r="H34" s="73">
+      <c r="H34" s="69">
         <f t="shared" ref="H34" si="14">(H33-G33)/G33</f>
         <v>0.15052380632378709</v>
       </c>
-      <c r="I34" s="73">
+      <c r="I34" s="69">
         <f t="shared" ref="I34" si="15">(I33-H33)/H33</f>
         <v>0.10948275862068949</v>
       </c>
-      <c r="J34" s="73">
+      <c r="J34" s="69">
         <f t="shared" ref="J34:K34" si="16">(J33-I33)/I33</f>
         <v>0.18109090909090922</v>
       </c>
-      <c r="K34" s="73">
+      <c r="K34" s="69">
         <f t="shared" si="16"/>
         <v>0.15448275862068975</v>
       </c>
-      <c r="L34" s="73">
+      <c r="L34" s="69">
         <f t="shared" ref="L34" si="17">(L33-K33)/K33</f>
         <v>5.199999999999997E-2</v>
       </c>
-      <c r="M34" s="73">
+      <c r="M34" s="69">
         <f t="shared" ref="M34" si="18">(M33-L33)/L33</f>
         <v>5.2000000000000275E-2</v>
       </c>
-      <c r="N34" s="100"/>
+      <c r="N34" s="87"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="100"/>
-      <c r="B35" s="51" t="s">
+      <c r="A35" s="87"/>
+      <c r="B35" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="71">
+      <c r="C35" s="67">
         <f>C33/C20</f>
         <v>0.31543013199817932</v>
       </c>
-      <c r="D35" s="71">
+      <c r="D35" s="67">
         <f>D33/D20</f>
         <v>-0.36969111969111967</v>
       </c>
-      <c r="E35" s="71">
+      <c r="E35" s="67">
         <f>E33/E20</f>
         <v>5.192943331607662E-2</v>
       </c>
-      <c r="F35" s="71">
+      <c r="F35" s="67">
         <f>F33/F20</f>
         <v>0.26138370164267749</v>
       </c>
-      <c r="G35" s="74">
+      <c r="G35" s="70">
         <v>0.42</v>
       </c>
-      <c r="H35" s="75">
+      <c r="H35" s="67">
         <v>0.4</v>
       </c>
-      <c r="I35" s="75">
+      <c r="I35" s="67">
         <v>0.35</v>
       </c>
-      <c r="J35" s="75">
+      <c r="J35" s="67">
         <v>0.35</v>
       </c>
-      <c r="K35" s="75">
+      <c r="K35" s="67">
         <v>0.35</v>
       </c>
-      <c r="L35" s="75">
+      <c r="L35" s="67">
         <v>0.35</v>
       </c>
-      <c r="M35" s="75">
+      <c r="M35" s="67">
         <v>0.35</v>
       </c>
-      <c r="N35" s="100"/>
+      <c r="N35" s="87"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="100"/>
-      <c r="G36" s="66"/>
-      <c r="H36" s="62"/>
-      <c r="I36" s="62"/>
-      <c r="J36" s="62"/>
-      <c r="K36" s="62"/>
-      <c r="L36" s="62"/>
-      <c r="M36" s="62"/>
-      <c r="N36" s="100"/>
+      <c r="A36" s="87"/>
+      <c r="G36" s="62"/>
+      <c r="N36" s="87"/>
     </row>
     <row r="37" spans="1:14" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="100"/>
-      <c r="B37" s="51" t="s">
+      <c r="A37" s="87"/>
+      <c r="B37" s="48" t="s">
         <v>121</v>
       </c>
-      <c r="C37" s="68">
+      <c r="C37" s="64">
         <f xml:space="preserve"> 'Income Statement'!F34</f>
         <v>16818</v>
       </c>
-      <c r="D37" s="68">
+      <c r="D37" s="64">
         <f xml:space="preserve"> 'Income Statement'!G34</f>
         <v>2011</v>
       </c>
-      <c r="E37" s="68">
+      <c r="E37" s="64">
         <f xml:space="preserve"> 'Income Statement'!H34</f>
         <v>9084</v>
       </c>
-      <c r="F37" s="68">
+      <c r="F37" s="64">
         <f xml:space="preserve"> 'Income Statement'!I34</f>
         <v>18122</v>
       </c>
-      <c r="G37" s="69">
+      <c r="G37" s="65">
         <f>G33+G41</f>
         <v>56838.786109999994</v>
       </c>
-      <c r="H37" s="70">
+      <c r="H37" s="66">
         <f t="shared" ref="H37:M37" si="19">H33+H41</f>
         <v>68997.902653680008</v>
       </c>
-      <c r="I37" s="70">
+      <c r="I37" s="66">
         <f t="shared" si="19"/>
         <v>79665.341550794998</v>
       </c>
-      <c r="J37" s="70">
+      <c r="J37" s="66">
         <f t="shared" si="19"/>
         <v>92794.189838366015</v>
       </c>
-      <c r="K37" s="70">
+      <c r="K37" s="66">
         <f t="shared" si="19"/>
         <v>105357.09553956019</v>
       </c>
-      <c r="L37" s="70">
+      <c r="L37" s="66">
         <f t="shared" si="19"/>
         <v>110835.66450761732</v>
       </c>
-      <c r="M37" s="70">
+      <c r="M37" s="66">
         <f t="shared" si="19"/>
         <v>116599.11906201344</v>
       </c>
-      <c r="N37" s="100"/>
+      <c r="N37" s="87"/>
     </row>
     <row r="38" spans="1:14" ht="20" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="100"/>
-      <c r="B38" s="51" t="s">
+      <c r="A38" s="87"/>
+      <c r="B38" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="72">
+      <c r="C38" s="68">
         <f>(C37-'Income Statement'!E34)/'Income Statement'!E34</f>
         <v>0.34576298311594783</v>
       </c>
-      <c r="D38" s="72">
+      <c r="D38" s="68">
         <f t="shared" ref="D38" si="20">(D37-C37)/C37</f>
         <v>-0.88042573433226301</v>
       </c>
-      <c r="E38" s="72">
+      <c r="E38" s="68">
         <f t="shared" ref="E38" si="21">(E37-D37)/D37</f>
         <v>3.5171556439582297</v>
       </c>
-      <c r="F38" s="72">
+      <c r="F38" s="68">
         <f t="shared" ref="F38" si="22">(F37-E37)/E37</f>
         <v>0.99493615147512104</v>
       </c>
-      <c r="G38" s="78">
+      <c r="G38" s="73">
         <f t="shared" ref="G38" si="23">(G37-F37)/F37</f>
         <v>2.1364521636684688</v>
       </c>
-      <c r="H38" s="73">
+      <c r="H38" s="69">
         <f t="shared" ref="H38" si="24">(H37-G37)/G37</f>
         <v>0.21392287513228203</v>
       </c>
-      <c r="I38" s="73">
+      <c r="I38" s="69">
         <f t="shared" ref="I38" si="25">(I37-H37)/H37</f>
         <v>0.15460526315789455</v>
       </c>
-      <c r="J38" s="73">
+      <c r="J38" s="69">
         <f t="shared" ref="J38" si="26">(J37-I37)/I37</f>
         <v>0.16480000000000003</v>
       </c>
-      <c r="K38" s="73">
+      <c r="K38" s="69">
         <f t="shared" ref="K38" si="27">(K37-J37)/J37</f>
         <v>0.13538461538461546</v>
       </c>
-      <c r="L38" s="73">
+      <c r="L38" s="69">
         <f t="shared" ref="L38" si="28">(L37-K37)/K37</f>
         <v>5.1999999999999935E-2</v>
       </c>
-      <c r="M38" s="73">
+      <c r="M38" s="69">
         <f t="shared" ref="M38" si="29">(M37-L37)/L37</f>
         <v>5.2000000000000254E-2</v>
       </c>
-      <c r="N38" s="100"/>
+      <c r="N38" s="87"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="100"/>
-      <c r="B39" s="51" t="s">
+      <c r="A39" s="87"/>
+      <c r="B39" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C39" s="71">
-        <f>C37/C20</f>
+      <c r="C39" s="67">
+        <f t="shared" ref="C39:M39" si="30">C37/C20</f>
         <v>0.54678457637037514</v>
       </c>
-      <c r="D39" s="71">
-        <f>D37/D20</f>
+      <c r="D39" s="67">
+        <f t="shared" si="30"/>
         <v>0.12940797940797941</v>
       </c>
-      <c r="E39" s="71">
-        <f>E37/E20</f>
+      <c r="E39" s="67">
+        <f t="shared" si="30"/>
         <v>0.36175381306996934</v>
       </c>
-      <c r="F39" s="71">
-        <f>F37/F20</f>
+      <c r="F39" s="67">
+        <f t="shared" si="30"/>
         <v>0.4848306490448927</v>
       </c>
-      <c r="G39" s="74">
-        <f>G37/G20</f>
+      <c r="G39" s="70">
+        <f t="shared" si="30"/>
         <v>0.77006539636888738</v>
       </c>
-      <c r="H39" s="75">
-        <f>H37/H20</f>
+      <c r="H39" s="67">
+        <f t="shared" si="30"/>
         <v>0.76000000000000012</v>
       </c>
-      <c r="I39" s="75">
-        <f>I37/I20</f>
+      <c r="I39" s="67">
+        <f t="shared" si="30"/>
         <v>0.75</v>
       </c>
-      <c r="J39" s="75">
-        <f>J37/J20</f>
+      <c r="J39" s="67">
+        <f t="shared" si="30"/>
         <v>0.77999999999999992</v>
       </c>
-      <c r="K39" s="75">
-        <f>K37/K20</f>
+      <c r="K39" s="67">
+        <f t="shared" si="30"/>
         <v>0.82</v>
       </c>
-      <c r="L39" s="75">
-        <f>L37/L20</f>
+      <c r="L39" s="67">
+        <f t="shared" si="30"/>
         <v>0.82</v>
       </c>
-      <c r="M39" s="75">
-        <f>M37/M20</f>
+      <c r="M39" s="67">
+        <f t="shared" si="30"/>
         <v>0.82000000000000006</v>
       </c>
-      <c r="N39" s="100"/>
+      <c r="N39" s="87"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="100"/>
-      <c r="C40" s="71"/>
-      <c r="D40" s="71"/>
-      <c r="E40" s="71"/>
-      <c r="F40" s="71"/>
-      <c r="G40" s="74"/>
-      <c r="H40" s="75"/>
-      <c r="I40" s="75"/>
-      <c r="J40" s="75"/>
-      <c r="K40" s="75"/>
-      <c r="L40" s="75"/>
-      <c r="M40" s="75"/>
-      <c r="N40" s="100"/>
+      <c r="A40" s="87"/>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="67"/>
+      <c r="I40" s="67"/>
+      <c r="J40" s="67"/>
+      <c r="K40" s="67"/>
+      <c r="L40" s="67"/>
+      <c r="M40" s="67"/>
+      <c r="N40" s="87"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="100"/>
-      <c r="B41" s="51" t="s">
+      <c r="A41" s="87"/>
+      <c r="B41" s="48" t="s">
         <v>123</v>
       </c>
-      <c r="C41" s="68">
+      <c r="C41" s="64">
         <f>'Cash Flow Statement'!F7</f>
         <v>7116</v>
       </c>
-      <c r="D41" s="68">
+      <c r="D41" s="64">
         <f>'Cash Flow Statement'!G7</f>
         <v>7756</v>
       </c>
-      <c r="E41" s="68">
+      <c r="E41" s="64">
         <f>'Cash Flow Statement'!H7</f>
         <v>7780</v>
       </c>
-      <c r="F41" s="68">
+      <c r="F41" s="64">
         <f>'Cash Flow Statement'!I7</f>
         <v>8352</v>
       </c>
-      <c r="G41" s="79">
-        <f>G20*G43</f>
+      <c r="G41" s="74">
+        <f t="shared" ref="G41:M41" si="31">G20*G43</f>
         <v>11071.55049</v>
       </c>
-      <c r="H41" s="80">
-        <f>H20*H43</f>
+      <c r="H41" s="75">
+        <f t="shared" si="31"/>
         <v>16341.60852324</v>
       </c>
-      <c r="I41" s="80">
-        <f>I20*I43</f>
+      <c r="I41" s="75">
+        <f t="shared" si="31"/>
         <v>21244.091080212002</v>
       </c>
-      <c r="J41" s="80">
-        <f>J20*J43</f>
+      <c r="J41" s="75">
+        <f t="shared" si="31"/>
         <v>23793.382009837442</v>
       </c>
-      <c r="K41" s="80">
-        <f>K20*K43</f>
+      <c r="K41" s="75">
+        <f t="shared" si="31"/>
         <v>25696.85257062444</v>
       </c>
-      <c r="L41" s="80">
-        <f>L20*L43</f>
+      <c r="L41" s="75">
+        <f t="shared" si="31"/>
         <v>27033.08890429691</v>
       </c>
-      <c r="M41" s="80">
-        <f>M20*M43</f>
+      <c r="M41" s="75">
+        <f t="shared" si="31"/>
         <v>28438.809527320351</v>
       </c>
-      <c r="N41" s="100"/>
+      <c r="N41" s="87"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="100"/>
-      <c r="B42" s="51" t="s">
+      <c r="A42" s="87"/>
+      <c r="B42" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C42" s="72">
+      <c r="C42" s="68">
         <f>(C41-'Income Statement'!E8)/'Income Statement'!E8</f>
         <v>0.14515609913099453</v>
       </c>
-      <c r="D42" s="72">
-        <f t="shared" ref="D42" si="30">(D41-C41)/C41</f>
+      <c r="D42" s="68">
+        <f t="shared" ref="D42" si="32">(D41-C41)/C41</f>
         <v>8.9938167509836991E-2</v>
       </c>
-      <c r="E42" s="72">
-        <f t="shared" ref="E42" si="31">(E41-D41)/D41</f>
+      <c r="E42" s="68">
+        <f t="shared" ref="E42" si="33">(E41-D41)/D41</f>
         <v>3.0943785456420837E-3</v>
       </c>
-      <c r="F42" s="72">
-        <f t="shared" ref="F42" si="32">(F41-E41)/E41</f>
+      <c r="F42" s="68">
+        <f t="shared" ref="F42" si="34">(F41-E41)/E41</f>
         <v>7.3521850899742933E-2</v>
       </c>
-      <c r="G42" s="78">
-        <f t="shared" ref="G42" si="33">(G41-F41)/F41</f>
+      <c r="G42" s="73">
+        <f t="shared" ref="G42" si="35">(G41-F41)/F41</f>
         <v>0.3256166774425287</v>
       </c>
-      <c r="H42" s="73">
-        <f t="shared" ref="H42" si="34">(H41-G41)/G41</f>
+      <c r="H42" s="69">
+        <f t="shared" ref="H42" si="36">(H41-G41)/G41</f>
         <v>0.47600000000000003</v>
       </c>
-      <c r="I42" s="73">
-        <f t="shared" ref="I42" si="35">(I41-H41)/H41</f>
+      <c r="I42" s="69">
+        <f t="shared" ref="I42" si="37">(I41-H41)/H41</f>
         <v>0.3000000000000001</v>
       </c>
-      <c r="J42" s="73">
-        <f t="shared" ref="J42" si="36">(J41-I41)/I41</f>
+      <c r="J42" s="69">
+        <f t="shared" ref="J42" si="38">(J41-I41)/I41</f>
         <v>0.12</v>
       </c>
-      <c r="K42" s="73">
-        <f t="shared" ref="K42" si="37">(K41-J41)/J41</f>
+      <c r="K42" s="69">
+        <f t="shared" ref="K42" si="39">(K41-J41)/J41</f>
         <v>8.0000000000000127E-2</v>
       </c>
-      <c r="L42" s="73">
-        <f t="shared" ref="L42" si="38">(L41-K41)/K41</f>
+      <c r="L42" s="69">
+        <f t="shared" ref="L42" si="40">(L41-K41)/K41</f>
         <v>5.1999999999999977E-2</v>
       </c>
-      <c r="M42" s="73">
-        <f t="shared" ref="M42" si="39">(M41-L41)/L41</f>
+      <c r="M42" s="69">
+        <f t="shared" ref="M42" si="41">(M41-L41)/L41</f>
         <v>5.2000000000000046E-2</v>
       </c>
-      <c r="N42" s="100"/>
+      <c r="N42" s="87"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="100"/>
-      <c r="B43" s="51" t="s">
+      <c r="A43" s="87"/>
+      <c r="B43" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C43" s="71">
+      <c r="C43" s="67">
         <f>C41/C20</f>
         <v>0.23135444437219585</v>
       </c>
-      <c r="D43" s="71">
+      <c r="D43" s="67">
         <f>D41/D20</f>
         <v>0.49909909909909911</v>
       </c>
-      <c r="E43" s="71">
+      <c r="E43" s="67">
         <f>E41/E20</f>
         <v>0.30982437975389271</v>
       </c>
-      <c r="F43" s="71">
+      <c r="F43" s="67">
         <f>F41/F20</f>
         <v>0.22344694740221521</v>
       </c>
-      <c r="G43" s="74">
+      <c r="G43" s="70">
         <v>0.15</v>
       </c>
-      <c r="H43" s="75">
+      <c r="H43" s="67">
         <v>0.18</v>
       </c>
-      <c r="I43" s="75">
+      <c r="I43" s="67">
         <v>0.2</v>
       </c>
-      <c r="J43" s="75">
+      <c r="J43" s="67">
         <v>0.2</v>
       </c>
-      <c r="K43" s="75">
+      <c r="K43" s="67">
         <v>0.2</v>
       </c>
-      <c r="L43" s="75">
+      <c r="L43" s="67">
         <v>0.2</v>
       </c>
-      <c r="M43" s="75">
+      <c r="M43" s="67">
         <v>0.2</v>
       </c>
-      <c r="N43" s="100"/>
+      <c r="N43" s="87"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="100"/>
-      <c r="C44" s="71"/>
-      <c r="D44" s="71"/>
-      <c r="E44" s="71"/>
-      <c r="F44" s="71"/>
-      <c r="G44" s="74"/>
-      <c r="H44" s="75"/>
-      <c r="I44" s="75"/>
-      <c r="J44" s="75"/>
-      <c r="K44" s="75"/>
-      <c r="L44" s="75"/>
-      <c r="M44" s="75"/>
-      <c r="N44" s="100"/>
+      <c r="A44" s="87"/>
+      <c r="C44" s="67"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="67"/>
+      <c r="F44" s="67"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="67"/>
+      <c r="I44" s="67"/>
+      <c r="J44" s="67"/>
+      <c r="K44" s="67"/>
+      <c r="L44" s="67"/>
+      <c r="M44" s="67"/>
+      <c r="N44" s="87"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="100"/>
-      <c r="B45" s="51" t="s">
+      <c r="A45" s="87"/>
+      <c r="B45" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="C45" s="68">
+      <c r="C45" s="64">
         <f>'Cash Flow Statement'!F19</f>
         <v>-12067</v>
       </c>
-      <c r="D45" s="68">
+      <c r="D45" s="64">
         <f>'Cash Flow Statement'!G19</f>
         <v>-7676</v>
       </c>
-      <c r="E45" s="68">
+      <c r="E45" s="64">
         <f>'Cash Flow Statement'!H19</f>
         <v>-8386</v>
       </c>
-      <c r="F45" s="68">
+      <c r="F45" s="64">
         <f>'Cash Flow Statement'!I19</f>
         <v>-15857</v>
       </c>
-      <c r="G45" s="79">
-        <f>G20*G47</f>
+      <c r="G45" s="74">
+        <f t="shared" ref="G45:M45" si="42">G20*G47</f>
         <v>20666.894248000001</v>
       </c>
-      <c r="H45" s="80">
-        <f>H20*H47</f>
+      <c r="H45" s="75">
+        <f t="shared" si="42"/>
         <v>27236.014205399999</v>
       </c>
-      <c r="I45" s="80">
-        <f>I20*I47</f>
+      <c r="I45" s="75">
+        <f t="shared" si="42"/>
         <v>33990.545728339202</v>
       </c>
-      <c r="J45" s="80">
-        <f>J20*J47</f>
+      <c r="J45" s="75">
+        <f t="shared" si="42"/>
         <v>38069.411215739907</v>
       </c>
-      <c r="K45" s="80">
-        <f>K20*K47</f>
+      <c r="K45" s="75">
+        <f t="shared" si="42"/>
         <v>41114.964112999107</v>
       </c>
-      <c r="L45" s="80">
-        <f>L20*L47</f>
+      <c r="L45" s="75">
+        <f t="shared" si="42"/>
         <v>43252.942246875056</v>
       </c>
-      <c r="M45" s="80">
-        <f>M20*M47</f>
+      <c r="M45" s="75">
+        <f t="shared" si="42"/>
         <v>45502.09524371256</v>
       </c>
-      <c r="N45" s="100"/>
+      <c r="N45" s="87"/>
     </row>
     <row r="46" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="100"/>
-      <c r="B46" s="81" t="s">
+      <c r="A46" s="87"/>
+      <c r="B46" s="76" t="s">
         <v>124</v>
       </c>
-      <c r="C46" s="72">
+      <c r="C46" s="68">
         <f>(C45-'Cash Flow Statement'!E19)/'Cash Flow Statement'!E19</f>
         <v>0.20309072781655035</v>
       </c>
-      <c r="D46" s="72">
-        <f t="shared" ref="D46" si="40">(D45-C45)/C45</f>
+      <c r="D46" s="68">
+        <f t="shared" ref="D46" si="43">(D45-C45)/C45</f>
         <v>-0.36388497555316152</v>
       </c>
-      <c r="E46" s="72">
-        <f t="shared" ref="E46" si="41">(E45-D45)/D45</f>
+      <c r="E46" s="68">
+        <f t="shared" ref="E46" si="44">(E45-D45)/D45</f>
         <v>9.2496091714434597E-2</v>
       </c>
-      <c r="F46" s="72">
-        <f t="shared" ref="F46" si="42">(F45-E45)/E45</f>
+      <c r="F46" s="68">
+        <f t="shared" ref="F46" si="45">(F45-E45)/E45</f>
         <v>0.89088957786787504</v>
       </c>
-      <c r="G46" s="78">
-        <f t="shared" ref="G46" si="43">(G45-F45)/F45</f>
+      <c r="G46" s="73">
+        <f t="shared" ref="G46" si="46">(G45-F45)/F45</f>
         <v>-2.3033293969855584</v>
       </c>
-      <c r="H46" s="73">
-        <f t="shared" ref="H46" si="44">(H45-G45)/G45</f>
+      <c r="H46" s="69">
+        <f t="shared" ref="H46" si="47">(H45-G45)/G45</f>
         <v>0.31785714285714278</v>
       </c>
-      <c r="I46" s="73">
-        <f t="shared" ref="I46" si="45">(I45-H45)/H45</f>
+      <c r="I46" s="69">
+        <f t="shared" ref="I46" si="48">(I45-H45)/H45</f>
         <v>0.24800000000000014</v>
       </c>
-      <c r="J46" s="73">
-        <f t="shared" ref="J46" si="46">(J45-I45)/I45</f>
+      <c r="J46" s="69">
+        <f t="shared" ref="J46" si="49">(J45-I45)/I45</f>
         <v>0.12</v>
       </c>
-      <c r="K46" s="73">
-        <f t="shared" ref="K46" si="47">(K45-J45)/J45</f>
+      <c r="K46" s="69">
+        <f t="shared" ref="K46" si="50">(K45-J45)/J45</f>
         <v>8.0000000000000196E-2</v>
       </c>
-      <c r="L46" s="73">
-        <f t="shared" ref="L46" si="48">(L45-K45)/K45</f>
+      <c r="L46" s="69">
+        <f t="shared" ref="L46" si="51">(L45-K45)/K45</f>
         <v>5.19999999999999E-2</v>
       </c>
-      <c r="M46" s="73">
-        <f t="shared" ref="M46" si="49">(M45-L45)/L45</f>
+      <c r="M46" s="69">
+        <f t="shared" ref="M46" si="52">(M45-L45)/L45</f>
         <v>5.2000000000000011E-2</v>
       </c>
-      <c r="N46" s="100"/>
+      <c r="N46" s="87"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="100"/>
-      <c r="B47" s="51" t="s">
+      <c r="A47" s="87"/>
+      <c r="B47" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="C47" s="71">
+      <c r="C47" s="67">
         <f>C45/-C20</f>
         <v>0.39232069705442485</v>
       </c>
-      <c r="D47" s="71">
+      <c r="D47" s="67">
         <f>D45/-D20</f>
         <v>0.49395109395109393</v>
       </c>
-      <c r="E47" s="71">
+      <c r="E47" s="67">
         <f>E45/-E20</f>
         <v>0.33395722989924737</v>
       </c>
-      <c r="F47" s="71">
+      <c r="F47" s="67">
         <f>F45/-F20</f>
         <v>0.42423350634062817</v>
       </c>
-      <c r="G47" s="74">
+      <c r="G47" s="70">
         <v>0.28000000000000003</v>
       </c>
-      <c r="H47" s="75">
+      <c r="H47" s="67">
         <v>0.3</v>
       </c>
-      <c r="I47" s="75">
+      <c r="I47" s="67">
         <v>0.32</v>
       </c>
-      <c r="J47" s="75">
+      <c r="J47" s="67">
         <v>0.32</v>
       </c>
-      <c r="K47" s="75">
+      <c r="K47" s="67">
         <v>0.32</v>
       </c>
-      <c r="L47" s="75">
+      <c r="L47" s="67">
         <v>0.32</v>
       </c>
-      <c r="M47" s="75">
+      <c r="M47" s="67">
         <v>0.32</v>
       </c>
-      <c r="N47" s="100"/>
+      <c r="N47" s="87"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="100"/>
-      <c r="C48" s="71"/>
-      <c r="D48" s="71"/>
-      <c r="E48" s="71"/>
-      <c r="F48" s="71"/>
-      <c r="G48" s="74"/>
-      <c r="H48" s="75"/>
-      <c r="I48" s="75"/>
-      <c r="J48" s="75"/>
-      <c r="K48" s="75"/>
-      <c r="L48" s="75"/>
-      <c r="M48" s="75"/>
-      <c r="N48" s="100"/>
+      <c r="A48" s="87"/>
+      <c r="C48" s="67"/>
+      <c r="D48" s="67"/>
+      <c r="E48" s="67"/>
+      <c r="F48" s="67"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="67"/>
+      <c r="I48" s="67"/>
+      <c r="J48" s="67"/>
+      <c r="K48" s="67"/>
+      <c r="L48" s="67"/>
+      <c r="M48" s="67"/>
+      <c r="N48" s="87"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="100"/>
-      <c r="B49" s="51" t="s">
+      <c r="A49" s="87"/>
+      <c r="B49" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="C49" s="68">
+      <c r="C49" s="64">
         <f>'Cash Flow Statement'!F11</f>
         <v>-1263</v>
       </c>
-      <c r="D49" s="68">
+      <c r="D49" s="64">
         <f>'Cash Flow Statement'!G11</f>
         <v>-2892</v>
       </c>
-      <c r="E49" s="68">
+      <c r="E49" s="64">
         <f>'Cash Flow Statement'!H11</f>
         <v>-884</v>
       </c>
-      <c r="F49" s="68">
+      <c r="F49" s="64">
         <f>'Cash Flow Statement'!I11</f>
         <v>-338</v>
       </c>
-      <c r="G49" s="79">
-        <f>G20*G50</f>
+      <c r="G49" s="74">
+        <f t="shared" ref="G49:M49" si="53">G20*G50</f>
         <v>-1476.2067319999999</v>
       </c>
-      <c r="H49" s="80">
-        <f>H20*H50</f>
+      <c r="H49" s="75">
+        <f t="shared" si="53"/>
         <v>-1815.73428036</v>
       </c>
-      <c r="I49" s="80">
-        <f>I20*I50</f>
+      <c r="I49" s="75">
+        <f t="shared" si="53"/>
         <v>-2124.4091080212002</v>
       </c>
-      <c r="J49" s="80">
-        <f>J20*J50</f>
+      <c r="J49" s="75">
+        <f t="shared" si="53"/>
         <v>-2379.3382009837442</v>
       </c>
-      <c r="K49" s="80">
-        <f>K20*K50</f>
+      <c r="K49" s="75">
+        <f t="shared" si="53"/>
         <v>-2569.6852570624442</v>
       </c>
-      <c r="L49" s="80">
-        <f>L20*L50</f>
+      <c r="L49" s="75">
+        <f t="shared" si="53"/>
         <v>-2703.308890429691</v>
       </c>
-      <c r="M49" s="80">
-        <f>M20*M50</f>
+      <c r="M49" s="75">
+        <f t="shared" si="53"/>
         <v>-2843.880952732035</v>
       </c>
-      <c r="N49" s="100"/>
+      <c r="N49" s="87"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="100"/>
-      <c r="B50" s="51" t="s">
+      <c r="A50" s="87"/>
+      <c r="B50" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="71">
+      <c r="C50" s="67">
         <f>C49/-C20</f>
         <v>4.1062487808049941E-2</v>
       </c>
-      <c r="D50" s="71">
+      <c r="D50" s="67">
         <f>D49/-D20</f>
         <v>0.18610038610038609</v>
       </c>
-      <c r="E50" s="71">
+      <c r="E50" s="67">
         <f>E49/-E20</f>
         <v>3.5203695591573415E-2</v>
       </c>
-      <c r="F50" s="71">
+      <c r="F50" s="67">
         <f>F49/-F20</f>
         <v>9.0427524212103368E-3</v>
       </c>
-      <c r="G50" s="74">
+      <c r="G50" s="70">
         <v>-0.02</v>
       </c>
-      <c r="H50" s="75">
+      <c r="H50" s="67">
         <v>-0.02</v>
       </c>
-      <c r="I50" s="75">
+      <c r="I50" s="67">
         <v>-0.02</v>
       </c>
-      <c r="J50" s="75">
+      <c r="J50" s="67">
         <v>-0.02</v>
       </c>
-      <c r="K50" s="75">
+      <c r="K50" s="67">
         <v>-0.02</v>
       </c>
-      <c r="L50" s="75">
+      <c r="L50" s="67">
         <v>-0.02</v>
       </c>
-      <c r="M50" s="75">
+      <c r="M50" s="67">
         <v>-0.02</v>
       </c>
-      <c r="N50" s="100"/>
+      <c r="N50" s="87"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="100"/>
-      <c r="C51" s="71"/>
-      <c r="D51" s="71"/>
-      <c r="E51" s="71"/>
-      <c r="F51" s="71"/>
-      <c r="G51" s="74"/>
-      <c r="H51" s="75"/>
-      <c r="I51" s="75"/>
-      <c r="J51" s="75"/>
-      <c r="K51" s="75"/>
-      <c r="L51" s="75"/>
-      <c r="M51" s="75"/>
-      <c r="N51" s="100"/>
+      <c r="A51" s="87"/>
+      <c r="C51" s="67"/>
+      <c r="D51" s="67"/>
+      <c r="E51" s="67"/>
+      <c r="F51" s="67"/>
+      <c r="G51" s="70"/>
+      <c r="H51" s="67"/>
+      <c r="I51" s="67"/>
+      <c r="J51" s="67"/>
+      <c r="K51" s="67"/>
+      <c r="L51" s="67"/>
+      <c r="M51" s="67"/>
+      <c r="N51" s="87"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="100"/>
-      <c r="B52" s="51" t="s">
+      <c r="A52" s="87"/>
+      <c r="B52" s="48" t="s">
         <v>78</v>
       </c>
-      <c r="C52" s="82">
+      <c r="C52" s="72">
         <f>'Income Statement'!F24</f>
         <v>-888</v>
       </c>
-      <c r="D52" s="82">
+      <c r="D52" s="72">
         <f>'Income Statement'!G24</f>
         <v>-177</v>
       </c>
-      <c r="E52" s="82">
+      <c r="E52" s="72">
         <f>'Income Statement'!H24</f>
         <v>-451</v>
       </c>
-      <c r="F52" s="82">
+      <c r="F52" s="72">
         <f>'Income Statement'!I24</f>
         <v>-1124</v>
       </c>
-      <c r="G52" s="79">
-        <f>G20*G53</f>
+      <c r="G52" s="74">
+        <f t="shared" ref="G52:M52" si="54">G20*G53</f>
         <v>11440.602172999999</v>
       </c>
-      <c r="H52" s="80">
-        <f>H20*H53</f>
+      <c r="H52" s="75">
+        <f t="shared" si="54"/>
         <v>19065.209943779999</v>
       </c>
-      <c r="I52" s="80">
-        <f>I20*I53</f>
+      <c r="I52" s="75">
+        <f t="shared" si="54"/>
         <v>22306.295634222599</v>
       </c>
-      <c r="J52" s="80">
-        <f>J20*J53</f>
+      <c r="J52" s="75">
+        <f t="shared" si="54"/>
         <v>24983.051110329314</v>
       </c>
-      <c r="K52" s="80">
-        <f>K20*K53</f>
+      <c r="K52" s="75">
+        <f t="shared" si="54"/>
         <v>26981.69519915566</v>
       </c>
-      <c r="L52" s="80">
-        <f>L20*L53</f>
+      <c r="L52" s="75">
+        <f t="shared" si="54"/>
         <v>28384.743349511755</v>
       </c>
-      <c r="M52" s="80">
-        <f>M20*M53</f>
+      <c r="M52" s="75">
+        <f t="shared" si="54"/>
         <v>29860.750003686368</v>
       </c>
-      <c r="N52" s="100"/>
+      <c r="N52" s="87"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="100"/>
-      <c r="B53" s="51" t="s">
+      <c r="A53" s="87"/>
+      <c r="B53" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="C53" s="83"/>
-      <c r="D53" s="83"/>
-      <c r="E53" s="83"/>
-      <c r="F53" s="83"/>
-      <c r="G53" s="74">
+      <c r="C53" s="77"/>
+      <c r="D53" s="77"/>
+      <c r="E53" s="77"/>
+      <c r="F53" s="77"/>
+      <c r="G53" s="70">
         <v>0.155</v>
       </c>
-      <c r="H53" s="75">
+      <c r="H53" s="67">
         <v>0.21</v>
       </c>
-      <c r="I53" s="75">
+      <c r="I53" s="67">
         <v>0.21</v>
       </c>
-      <c r="J53" s="75">
+      <c r="J53" s="67">
         <v>0.21</v>
       </c>
-      <c r="K53" s="75">
+      <c r="K53" s="67">
         <v>0.21</v>
       </c>
-      <c r="L53" s="75">
+      <c r="L53" s="67">
         <v>0.21</v>
       </c>
-      <c r="M53" s="75">
+      <c r="M53" s="67">
         <v>0.21</v>
       </c>
-      <c r="N53" s="100"/>
+      <c r="N53" s="87"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="100"/>
-      <c r="G54" s="66"/>
-      <c r="H54" s="62"/>
-      <c r="I54" s="62"/>
-      <c r="J54" s="62"/>
-      <c r="K54" s="62"/>
-      <c r="L54" s="62"/>
-      <c r="M54" s="62"/>
-      <c r="N54" s="100"/>
+      <c r="A54" s="87"/>
+      <c r="G54" s="62"/>
+      <c r="N54" s="87"/>
     </row>
     <row r="55" spans="1:14" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="100"/>
-      <c r="B55" s="51" t="s">
+      <c r="A55" s="87"/>
+      <c r="B55" s="48" t="s">
         <v>122</v>
       </c>
-      <c r="C55" s="68">
+      <c r="C55" s="64">
         <f>'Income Statement'!F26</f>
         <v>8687</v>
       </c>
-      <c r="D55" s="68">
+      <c r="D55" s="64">
         <f>'Income Statement'!G26</f>
         <v>-5833</v>
       </c>
-      <c r="E55" s="68">
+      <c r="E55" s="64">
         <f>'Income Statement'!H26</f>
         <v>778</v>
       </c>
-      <c r="F55" s="68">
+      <c r="F55" s="64">
         <f>'Income Statement'!I26</f>
         <v>8539</v>
       </c>
-      <c r="G55" s="69">
-        <f>G33*(1-G53)</f>
+      <c r="G55" s="65">
+        <f t="shared" ref="G55:M55" si="55">G33*(1-G53)</f>
         <v>38673.314098899995</v>
       </c>
-      <c r="H55" s="70">
-        <f>H33*(1-H53)</f>
+      <c r="H55" s="66">
+        <f t="shared" si="55"/>
         <v>41598.4723630476</v>
       </c>
-      <c r="I55" s="70">
-        <f>I33*(1-I53)</f>
+      <c r="I55" s="66">
+        <f t="shared" si="55"/>
         <v>46152.787871760564</v>
       </c>
-      <c r="J55" s="70">
-        <f>J33*(1-J53)</f>
+      <c r="J55" s="66">
+        <f t="shared" si="55"/>
         <v>54510.638184537573</v>
       </c>
-      <c r="K55" s="70">
-        <f>K33*(1-K53)</f>
+      <c r="K55" s="66">
+        <f t="shared" si="55"/>
         <v>62931.591945459244</v>
       </c>
-      <c r="L55" s="70">
-        <f>L33*(1-L53)</f>
+      <c r="L55" s="66">
+        <f t="shared" si="55"/>
         <v>66204.034726623126</v>
       </c>
-      <c r="M55" s="70">
-        <f>M33*(1-M53)</f>
+      <c r="M55" s="66">
+        <f t="shared" si="55"/>
         <v>69646.644532407547</v>
       </c>
-      <c r="N55" s="100"/>
+      <c r="N55" s="87"/>
     </row>
     <row r="56" spans="1:14" ht="20" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="100"/>
-      <c r="B56" s="51" t="s">
+      <c r="A56" s="87"/>
+      <c r="B56" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C56" s="84">
+      <c r="C56" s="68">
         <f>(C55-'Income Statement'!E26)/'Income Statement'!E26</f>
         <v>0.48217027810953761</v>
       </c>
-      <c r="D56" s="84">
+      <c r="D56" s="68">
         <f>(D55-C55)/C55</f>
         <v>-1.6714631057902614</v>
       </c>
-      <c r="E56" s="84">
-        <f t="shared" ref="E56:M56" si="50">(E55-D55)/D55</f>
+      <c r="E56" s="68">
+        <f t="shared" ref="E56:M56" si="56">(E55-D55)/D55</f>
         <v>-1.1333790502314418</v>
       </c>
-      <c r="F56" s="84">
-        <f t="shared" si="50"/>
+      <c r="F56" s="68">
+        <f t="shared" si="56"/>
         <v>9.9755784061696655</v>
       </c>
-      <c r="G56" s="85">
-        <f t="shared" si="50"/>
+      <c r="G56" s="73">
+        <f t="shared" si="56"/>
         <v>3.5290214426630748</v>
       </c>
-      <c r="H56" s="86">
-        <f t="shared" si="50"/>
+      <c r="H56" s="69">
+        <f t="shared" si="56"/>
         <v>7.5637641415138165E-2</v>
       </c>
-      <c r="I56" s="86">
-        <f t="shared" si="50"/>
+      <c r="I56" s="69">
+        <f t="shared" si="56"/>
         <v>0.1094827586206895</v>
       </c>
-      <c r="J56" s="86">
-        <f t="shared" si="50"/>
+      <c r="J56" s="69">
+        <f t="shared" si="56"/>
         <v>0.18109090909090919</v>
       </c>
-      <c r="K56" s="86">
-        <f t="shared" si="50"/>
+      <c r="K56" s="69">
+        <f t="shared" si="56"/>
         <v>0.15448275862068975</v>
       </c>
-      <c r="L56" s="86">
-        <f t="shared" si="50"/>
+      <c r="L56" s="69">
+        <f t="shared" si="56"/>
         <v>5.2000000000000011E-2</v>
       </c>
-      <c r="M56" s="86">
-        <f t="shared" si="50"/>
+      <c r="M56" s="69">
+        <f t="shared" si="56"/>
         <v>5.2000000000000282E-2</v>
       </c>
-      <c r="N56" s="100"/>
+      <c r="N56" s="87"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="100"/>
-      <c r="B57" s="51" t="s">
+      <c r="A57" s="87"/>
+      <c r="B57" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C57" s="71">
-        <f>C55/C20</f>
+      <c r="C57" s="67">
+        <f t="shared" ref="C57:M57" si="57">C55/C20</f>
         <v>0.28243058716431496</v>
       </c>
-      <c r="D57" s="71">
-        <f>D55/D20</f>
+      <c r="D57" s="67">
+        <f t="shared" si="57"/>
         <v>-0.37535392535392537</v>
       </c>
-      <c r="E57" s="71">
-        <f>E55/E20</f>
+      <c r="E57" s="67">
+        <f t="shared" si="57"/>
         <v>3.0982437975389271E-2</v>
       </c>
-      <c r="F57" s="71">
-        <f>F55/F20</f>
+      <c r="F57" s="67">
+        <f t="shared" si="57"/>
         <v>0.22844989030980792</v>
       </c>
-      <c r="G57" s="74">
-        <f>G55/G20</f>
+      <c r="G57" s="70">
+        <f t="shared" si="57"/>
         <v>0.52395525993170988</v>
       </c>
-      <c r="H57" s="75">
-        <f>H55/H20</f>
+      <c r="H57" s="67">
+        <f t="shared" si="57"/>
         <v>0.4582</v>
       </c>
-      <c r="I57" s="75">
-        <f>I55/I20</f>
+      <c r="I57" s="67">
+        <f t="shared" si="57"/>
         <v>0.43449999999999994</v>
       </c>
-      <c r="J57" s="75">
-        <f>J55/J20</f>
+      <c r="J57" s="67">
+        <f t="shared" si="57"/>
         <v>0.45819999999999994</v>
       </c>
-      <c r="K57" s="75">
-        <f>K55/K20</f>
+      <c r="K57" s="67">
+        <f t="shared" si="57"/>
         <v>0.4897999999999999</v>
       </c>
-      <c r="L57" s="75">
-        <f>L55/L20</f>
+      <c r="L57" s="67">
+        <f t="shared" si="57"/>
         <v>0.48979999999999996</v>
       </c>
-      <c r="M57" s="75">
-        <f>M55/M20</f>
+      <c r="M57" s="67">
+        <f t="shared" si="57"/>
         <v>0.48980000000000007</v>
       </c>
-      <c r="N57" s="100"/>
+      <c r="N57" s="87"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="100"/>
-      <c r="G58" s="66"/>
-      <c r="H58" s="62"/>
-      <c r="I58" s="62"/>
-      <c r="J58" s="62"/>
-      <c r="K58" s="62"/>
-      <c r="L58" s="62"/>
-      <c r="M58" s="62"/>
-      <c r="N58" s="100"/>
+      <c r="A58" s="87"/>
+      <c r="G58" s="62"/>
+      <c r="N58" s="87"/>
     </row>
     <row r="59" spans="1:14" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="100"/>
-      <c r="B59" s="51" t="s">
+      <c r="A59" s="87"/>
+      <c r="B59" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="C59" s="68">
+      <c r="C59" s="64">
         <f>'Cash Flow Statement'!F40</f>
         <v>1851</v>
       </c>
-      <c r="D59" s="68">
+      <c r="D59" s="64">
         <f>'Cash Flow Statement'!G40</f>
         <v>-9009</v>
       </c>
-      <c r="E59" s="68">
+      <c r="E59" s="64">
         <f>'Cash Flow Statement'!H40</f>
         <v>-763</v>
       </c>
-      <c r="F59" s="87">
+      <c r="F59" s="64">
         <f>'Cash Flow Statement'!I40</f>
         <v>1330</v>
       </c>
-      <c r="G59" s="69">
+      <c r="G59" s="65">
         <f>G55+G41-G45+G49</f>
         <v>27601.763608899997</v>
       </c>
-      <c r="H59" s="70">
-        <f t="shared" ref="H59:M59" si="51">H55+H41-H45+H49</f>
+      <c r="H59" s="66">
+        <f t="shared" ref="H59:M59" si="58">H55+H41-H45+H49</f>
         <v>28888.332400527601</v>
       </c>
-      <c r="I59" s="70">
-        <f t="shared" si="51"/>
+      <c r="I59" s="66">
+        <f t="shared" si="58"/>
         <v>31281.924115612164</v>
       </c>
-      <c r="J59" s="70">
-        <f t="shared" si="51"/>
+      <c r="J59" s="66">
+        <f t="shared" si="58"/>
         <v>37855.270777651363</v>
       </c>
-      <c r="K59" s="70">
-        <f t="shared" si="51"/>
+      <c r="K59" s="66">
+        <f t="shared" si="58"/>
         <v>44943.795146022137</v>
       </c>
-      <c r="L59" s="70">
-        <f t="shared" si="51"/>
+      <c r="L59" s="66">
+        <f t="shared" si="58"/>
         <v>47280.872493615287</v>
       </c>
-      <c r="M59" s="70">
-        <f t="shared" si="51"/>
+      <c r="M59" s="66">
+        <f t="shared" si="58"/>
         <v>49739.477863283304</v>
       </c>
-      <c r="N59" s="100"/>
+      <c r="N59" s="87"/>
     </row>
     <row r="60" spans="1:14" ht="20" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="100"/>
-      <c r="B60" s="51" t="s">
+      <c r="A60" s="87"/>
+      <c r="B60" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C60" s="72">
+      <c r="C60" s="68">
         <f>(C59-'Cash Flow Statement'!E40)/'Cash Flow Statement'!E40</f>
         <v>-7.3573573573573567E-2</v>
       </c>
-      <c r="D60" s="72">
+      <c r="D60" s="68">
         <f>(D59-C59)/C59</f>
         <v>-5.8670988654781198</v>
       </c>
-      <c r="E60" s="72">
-        <f t="shared" ref="E60" si="52">(E59-D59)/D59</f>
+      <c r="E60" s="68">
+        <f t="shared" ref="E60" si="59">(E59-D59)/D59</f>
         <v>-0.91530691530691533</v>
       </c>
-      <c r="F60" s="73">
+      <c r="F60" s="69">
         <f>(F59-E59)/E59</f>
         <v>-2.7431192660550461</v>
       </c>
-      <c r="G60" s="78">
-        <f t="shared" ref="G60:M60" si="53">(G59-F59)/F59</f>
+      <c r="G60" s="73">
+        <f t="shared" ref="G60:M60" si="60">(G59-F59)/F59</f>
         <v>19.753205720977441</v>
       </c>
-      <c r="H60" s="73">
-        <f t="shared" si="53"/>
+      <c r="H60" s="69">
+        <f t="shared" si="60"/>
         <v>4.6611832847259026E-2</v>
       </c>
-      <c r="I60" s="73">
-        <f t="shared" si="53"/>
+      <c r="I60" s="69">
+        <f t="shared" si="60"/>
         <v>8.2856693903205297E-2</v>
       </c>
-      <c r="J60" s="73">
-        <f t="shared" si="53"/>
+      <c r="J60" s="69">
+        <f t="shared" si="60"/>
         <v>0.21013242784380315</v>
       </c>
-      <c r="K60" s="73">
-        <f t="shared" si="53"/>
+      <c r="K60" s="69">
+        <f t="shared" si="60"/>
         <v>0.18725329981143946</v>
       </c>
-      <c r="L60" s="73">
-        <f t="shared" si="53"/>
+      <c r="L60" s="69">
+        <f t="shared" si="60"/>
         <v>5.1999999999999956E-2</v>
       </c>
-      <c r="M60" s="73">
-        <f t="shared" si="53"/>
+      <c r="M60" s="69">
+        <f t="shared" si="60"/>
         <v>5.2000000000000476E-2</v>
       </c>
-      <c r="N60" s="100"/>
+      <c r="N60" s="87"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="100"/>
-      <c r="B61" s="51" t="s">
+      <c r="A61" s="87"/>
+      <c r="B61" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C61" s="71">
-        <f>C59/C20</f>
+      <c r="C61" s="67">
+        <f t="shared" ref="C61:M61" si="61">C59/C20</f>
         <v>6.0179465504909289E-2</v>
       </c>
-      <c r="D61" s="71">
-        <f>D59/D20</f>
+      <c r="D61" s="67">
+        <f t="shared" si="61"/>
         <v>-0.57972972972972969</v>
       </c>
-      <c r="E61" s="71">
-        <f>E59/E20</f>
+      <c r="E61" s="67">
+        <f t="shared" si="61"/>
         <v>-3.0385090199514159E-2</v>
       </c>
-      <c r="F61" s="75">
-        <f>F59/F20</f>
+      <c r="F61" s="67">
+        <f t="shared" si="61"/>
         <v>3.5582428166301035E-2</v>
       </c>
-      <c r="G61" s="74">
-        <f>G59/G20</f>
+      <c r="G61" s="70">
+        <f t="shared" si="61"/>
         <v>0.37395525993170986</v>
       </c>
-      <c r="H61" s="75">
-        <f>H59/H20</f>
+      <c r="H61" s="67">
+        <f t="shared" si="61"/>
         <v>0.31820000000000004</v>
       </c>
-      <c r="I61" s="75">
-        <f>I59/I20</f>
+      <c r="I61" s="67">
+        <f t="shared" si="61"/>
         <v>0.29449999999999993</v>
       </c>
-      <c r="J61" s="75">
-        <f>J59/J20</f>
+      <c r="J61" s="67">
+        <f t="shared" si="61"/>
         <v>0.31819999999999993</v>
       </c>
-      <c r="K61" s="75">
-        <f>K59/K20</f>
+      <c r="K61" s="67">
+        <f t="shared" si="61"/>
         <v>0.34979999999999994</v>
       </c>
-      <c r="L61" s="75">
-        <f>L59/L20</f>
+      <c r="L61" s="67">
+        <f t="shared" si="61"/>
         <v>0.34979999999999994</v>
       </c>
-      <c r="M61" s="75">
-        <f>M59/M20</f>
+      <c r="M61" s="67">
+        <f t="shared" si="61"/>
         <v>0.34980000000000006</v>
       </c>
-      <c r="N61" s="100"/>
+      <c r="N61" s="87"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="100"/>
-      <c r="B62" s="100"/>
-      <c r="C62" s="102"/>
-      <c r="D62" s="102"/>
-      <c r="E62" s="102"/>
-      <c r="F62" s="103"/>
-      <c r="G62" s="104"/>
-      <c r="H62" s="103"/>
-      <c r="I62" s="103"/>
-      <c r="J62" s="103"/>
-      <c r="K62" s="103"/>
-      <c r="L62" s="103"/>
-      <c r="M62" s="103"/>
-      <c r="N62" s="100"/>
+      <c r="A62" s="87"/>
+      <c r="B62" s="87"/>
+      <c r="C62" s="89"/>
+      <c r="D62" s="89"/>
+      <c r="E62" s="89"/>
+      <c r="F62" s="89"/>
+      <c r="G62" s="90"/>
+      <c r="H62" s="89"/>
+      <c r="I62" s="89"/>
+      <c r="J62" s="89"/>
+      <c r="K62" s="89"/>
+      <c r="L62" s="89"/>
+      <c r="M62" s="89"/>
+      <c r="N62" s="87"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C63" s="71"/>
-      <c r="D63" s="71"/>
-      <c r="E63" s="71"/>
-      <c r="F63" s="75"/>
-      <c r="G63" s="74"/>
-      <c r="H63" s="75"/>
-      <c r="I63" s="75"/>
-      <c r="J63" s="75"/>
-      <c r="K63" s="75"/>
-      <c r="L63" s="75"/>
-      <c r="M63" s="75"/>
+      <c r="C63" s="67"/>
+      <c r="D63" s="67"/>
+      <c r="E63" s="67"/>
+      <c r="F63" s="67"/>
+      <c r="G63" s="70"/>
+      <c r="H63" s="67"/>
+      <c r="I63" s="67"/>
+      <c r="J63" s="67"/>
+      <c r="K63" s="67"/>
+      <c r="L63" s="67"/>
+      <c r="M63" s="67"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="88"/>
-      <c r="B64" s="88" t="s">
+      <c r="A64" s="78"/>
+      <c r="B64" s="78" t="s">
         <v>137</v>
       </c>
-      <c r="C64" s="89"/>
-      <c r="D64" s="89"/>
-      <c r="E64" s="89"/>
-      <c r="F64" s="90"/>
-      <c r="G64" s="91" t="s">
+      <c r="C64" s="79"/>
+      <c r="D64" s="79"/>
+      <c r="E64" s="79"/>
+      <c r="F64" s="79"/>
+      <c r="G64" s="80" t="s">
         <v>113</v>
       </c>
-      <c r="H64" s="92" t="s">
+      <c r="H64" s="81" t="s">
         <v>114</v>
       </c>
-      <c r="I64" s="92" t="s">
+      <c r="I64" s="81" t="s">
         <v>115</v>
       </c>
-      <c r="J64" s="92" t="s">
+      <c r="J64" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="K64" s="92" t="s">
+      <c r="K64" s="81" t="s">
         <v>117</v>
       </c>
-      <c r="L64" s="92" t="s">
+      <c r="L64" s="81" t="s">
         <v>118</v>
       </c>
-      <c r="M64" s="92" t="s">
+      <c r="M64" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="N64" s="88"/>
+      <c r="N64" s="78"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="88"/>
-      <c r="F65" s="62"/>
-      <c r="G65" s="66"/>
-      <c r="H65" s="62"/>
-      <c r="I65" s="62"/>
-      <c r="J65" s="62"/>
-      <c r="K65" s="62"/>
-      <c r="L65" s="62"/>
-      <c r="M65" s="62"/>
-      <c r="N65" s="88"/>
+      <c r="A65" s="78"/>
+      <c r="G65" s="62"/>
+      <c r="N65" s="78"/>
     </row>
     <row r="66" spans="1:14" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="88"/>
-      <c r="B66" s="51" t="s">
+      <c r="A66" s="78"/>
+      <c r="B66" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="F66" s="62"/>
-      <c r="G66" s="69">
+      <c r="G66" s="65">
         <f ca="1">G59*G68</f>
-        <v>26140.016454828299</v>
-      </c>
-      <c r="H66" s="70">
-        <f t="shared" ref="H66:M66" ca="1" si="54">H59*H68</f>
-        <v>24537.456696773552</v>
-      </c>
-      <c r="I66" s="70">
-        <f t="shared" ca="1" si="54"/>
-        <v>23830.797745706459</v>
-      </c>
-      <c r="J66" s="70">
-        <f t="shared" ca="1" si="54"/>
-        <v>25864.824066938927</v>
-      </c>
-      <c r="K66" s="70">
-        <f t="shared" ca="1" si="54"/>
-        <v>27541.713929044177</v>
-      </c>
-      <c r="L66" s="70">
-        <f t="shared" ca="1" si="54"/>
-        <v>25986.318191373124</v>
-      </c>
-      <c r="M66" s="70">
-        <f t="shared" ca="1" si="54"/>
-        <v>24518.762154128781</v>
-      </c>
-      <c r="N66" s="88"/>
+        <v>26110.048639100612</v>
+      </c>
+      <c r="H66" s="66">
+        <f t="shared" ref="H66:M66" ca="1" si="62">H59*H68</f>
+        <v>24453.161651444909</v>
+      </c>
+      <c r="I66" s="66">
+        <f t="shared" ca="1" si="62"/>
+        <v>23694.508358781048</v>
+      </c>
+      <c r="J66" s="66">
+        <f t="shared" ca="1" si="62"/>
+        <v>25657.970308045333</v>
+      </c>
+      <c r="K66" s="66">
+        <f t="shared" ca="1" si="62"/>
+        <v>27258.84066150037</v>
+      </c>
+      <c r="L66" s="66">
+        <f t="shared" ca="1" si="62"/>
+        <v>25660.482504462492</v>
+      </c>
+      <c r="M66" s="66">
+        <f t="shared" ca="1" si="62"/>
+        <v>24155.846190913653</v>
+      </c>
+      <c r="N66" s="78"/>
     </row>
     <row r="67" spans="1:14" ht="20" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="88"/>
-      <c r="B67" s="51" t="s">
+      <c r="A67" s="78"/>
+      <c r="B67" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="C67" s="93">
+      <c r="C67" s="82">
         <f ca="1" xml:space="preserve"> (M59 * (1 + $C$14)) / ($C$13- $C$14)</f>
-        <v>566686.18489910173</v>
-      </c>
-      <c r="F67" s="77"/>
-      <c r="G67" s="66"/>
-      <c r="H67" s="62"/>
-      <c r="I67" s="62"/>
-      <c r="J67" s="62"/>
-      <c r="K67" s="62"/>
-      <c r="L67" s="62"/>
-      <c r="M67" s="62"/>
-      <c r="N67" s="88"/>
+        <v>551002.09571443999</v>
+      </c>
+      <c r="F67" s="72"/>
+      <c r="G67" s="62"/>
+      <c r="N67" s="78"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="88"/>
-      <c r="B68" s="51" t="s">
+      <c r="A68" s="78"/>
+      <c r="B68" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="C68" s="71"/>
-      <c r="F68" s="75"/>
-      <c r="G68" s="66">
+      <c r="C68" s="67"/>
+      <c r="F68" s="67"/>
+      <c r="G68" s="62">
         <f ca="1" xml:space="preserve"> 1 / (1 + $C$13)^0.5</f>
-        <v>0.94704153057812701</v>
-      </c>
-      <c r="H68" s="62">
+        <v>0.94595580952956237</v>
+      </c>
+      <c r="H68" s="48">
         <f ca="1" xml:space="preserve"> 1 / (1 + $C$13)^1.5</f>
-        <v>0.84938986288891538</v>
-      </c>
-      <c r="I68" s="62">
+        <v>0.84647190126482719</v>
+      </c>
+      <c r="I68" s="48">
         <f ca="1" xml:space="preserve"> 1 / (1 + $C$13)^2.5</f>
-        <v>0.76180728709756695</v>
-      </c>
-      <c r="J68" s="62">
+        <v>0.75745047750932959</v>
+      </c>
+      <c r="J68" s="48">
         <f ca="1" xml:space="preserve"> 1 / (1 + $C$13)^3.5</f>
-        <v>0.6832555555832599</v>
-      </c>
-      <c r="K68" s="62">
+        <v>0.67779122381005508</v>
+      </c>
+      <c r="K68" s="48">
         <f ca="1" xml:space="preserve"> 1 / (1 + $C$13)^4.5</f>
-        <v>0.61280347686619041</v>
-      </c>
-      <c r="L68" s="62">
+        <v>0.60650954315131933</v>
+      </c>
+      <c r="L68" s="48">
         <f ca="1" xml:space="preserve"> 1 / (1 + $C$13)^5.5</f>
-        <v>0.54961587679842971</v>
-      </c>
-      <c r="M68" s="62">
+        <v>0.5427243862288631</v>
+      </c>
+      <c r="M68" s="48">
         <f ca="1" xml:space="preserve"> 1 / (1 + $C$13)^6.5</f>
-        <v>0.49294369799221488</v>
-      </c>
-      <c r="N68" s="88"/>
+        <v>0.48564736158489152</v>
+      </c>
+      <c r="N68" s="78"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="88"/>
-      <c r="B69" s="51" t="s">
+      <c r="A69" s="78"/>
+      <c r="B69" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="C69" s="93">
+      <c r="C69" s="82">
         <f ca="1">SUM(G66:M66)</f>
-        <v>178419.88923879332</v>
-      </c>
-      <c r="F69" s="77"/>
-      <c r="G69" s="66"/>
-      <c r="H69" s="62"/>
-      <c r="I69" s="62"/>
-      <c r="J69" s="62"/>
-      <c r="K69" s="62"/>
-      <c r="L69" s="62"/>
-      <c r="M69" s="62"/>
-      <c r="N69" s="88"/>
+        <v>176990.85831424844</v>
+      </c>
+      <c r="F69" s="72"/>
+      <c r="G69" s="62"/>
+      <c r="N69" s="78"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="88"/>
-      <c r="B70" s="51" t="s">
+      <c r="A70" s="78"/>
+      <c r="B70" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="C70" s="93">
+      <c r="C70" s="82">
         <f ca="1">C67/(1+$C$13)^7</f>
-        <v>264550.73258899123</v>
-      </c>
-      <c r="F70" s="77"/>
-      <c r="G70" s="66"/>
-      <c r="H70" s="62"/>
-      <c r="I70" s="62"/>
-      <c r="J70" s="62"/>
-      <c r="K70" s="62"/>
-      <c r="L70" s="62"/>
-      <c r="M70" s="62"/>
-      <c r="N70" s="88"/>
+        <v>253130.88240692674</v>
+      </c>
+      <c r="F70" s="72"/>
+      <c r="G70" s="62"/>
+      <c r="N70" s="78"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="88"/>
-      <c r="B71" s="51" t="s">
+      <c r="A71" s="78"/>
+      <c r="B71" s="48" t="s">
         <v>134</v>
       </c>
-      <c r="C71" s="93">
+      <c r="C71" s="82">
         <f ca="1">C70+C69</f>
-        <v>442970.62182778458</v>
-      </c>
-      <c r="F71" s="77"/>
-      <c r="G71" s="66"/>
-      <c r="H71" s="62"/>
-      <c r="I71" s="62"/>
-      <c r="J71" s="62"/>
-      <c r="K71" s="62"/>
-      <c r="L71" s="62"/>
-      <c r="M71" s="62"/>
-      <c r="N71" s="88"/>
+        <v>430121.74072117521</v>
+      </c>
+      <c r="F71" s="72"/>
+      <c r="G71" s="62"/>
+      <c r="N71" s="78"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="88"/>
-      <c r="B72" s="51" t="s">
+      <c r="A72" s="78"/>
+      <c r="B72" s="48" t="s">
         <v>135</v>
       </c>
-      <c r="C72" s="93">
+      <c r="C72" s="82">
         <f ca="1">C71-WACC!F20+9642+665</f>
-        <v>437925.62182778458</v>
-      </c>
-      <c r="F72" s="77"/>
-      <c r="G72" s="66"/>
-      <c r="H72" s="62"/>
-      <c r="I72" s="62"/>
-      <c r="J72" s="62"/>
-      <c r="K72" s="62"/>
-      <c r="L72" s="62"/>
-      <c r="M72" s="62"/>
-      <c r="N72" s="88"/>
+        <v>425076.74072117521</v>
+      </c>
+      <c r="F72" s="72"/>
+      <c r="G72" s="62"/>
+      <c r="N72" s="78"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="88"/>
-      <c r="B73" s="51" t="s">
+      <c r="A73" s="78"/>
+      <c r="B73" s="48" t="s">
         <v>136</v>
       </c>
-      <c r="C73" s="93">
+      <c r="C73" s="82">
         <f ca="1">C72/C5</f>
-        <v>390.14579183226857</v>
-      </c>
-      <c r="F73" s="77"/>
-      <c r="G73" s="66"/>
-      <c r="H73" s="62"/>
-      <c r="I73" s="62"/>
-      <c r="J73" s="62"/>
-      <c r="K73" s="62"/>
-      <c r="L73" s="62"/>
-      <c r="M73" s="62"/>
-      <c r="N73" s="88"/>
+        <v>378.69878657924386</v>
+      </c>
+      <c r="F73" s="72"/>
+      <c r="G73" s="62"/>
+      <c r="N73" s="78"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="88"/>
-      <c r="B74" s="88"/>
-      <c r="C74" s="88"/>
-      <c r="D74" s="88"/>
-      <c r="E74" s="88"/>
-      <c r="F74" s="88"/>
-      <c r="G74" s="99"/>
-      <c r="H74" s="99"/>
-      <c r="I74" s="99"/>
-      <c r="J74" s="99"/>
-      <c r="K74" s="99"/>
-      <c r="L74" s="99"/>
-      <c r="M74" s="99"/>
-      <c r="N74" s="88"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G75" s="62"/>
-      <c r="H75" s="62"/>
-      <c r="I75" s="62"/>
-      <c r="J75" s="62"/>
-      <c r="K75" s="62"/>
-      <c r="L75" s="62"/>
-      <c r="M75" s="62"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G76" s="62"/>
-      <c r="H76" s="62"/>
-      <c r="I76" s="62"/>
-      <c r="J76" s="62"/>
-      <c r="K76" s="62"/>
-      <c r="L76" s="62"/>
-      <c r="M76" s="62"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G77" s="62"/>
-      <c r="H77" s="62"/>
-      <c r="I77" s="62"/>
-      <c r="J77" s="62"/>
-      <c r="K77" s="62"/>
-      <c r="L77" s="62"/>
-      <c r="M77" s="62"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G78" s="62"/>
-      <c r="H78" s="62"/>
-      <c r="I78" s="62"/>
-      <c r="J78" s="62"/>
-      <c r="K78" s="62"/>
-      <c r="L78" s="62"/>
-      <c r="M78" s="62"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G79" s="62"/>
-      <c r="H79" s="62"/>
-      <c r="I79" s="62"/>
-      <c r="J79" s="62"/>
-      <c r="K79" s="62"/>
-      <c r="L79" s="62"/>
-      <c r="M79" s="62"/>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G80" s="62"/>
-      <c r="H80" s="62"/>
-      <c r="I80" s="62"/>
-      <c r="J80" s="62"/>
-      <c r="K80" s="62"/>
-      <c r="L80" s="62"/>
-      <c r="M80" s="62"/>
-    </row>
-    <row r="81" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G81" s="62"/>
-      <c r="H81" s="62"/>
-      <c r="I81" s="62"/>
-      <c r="J81" s="62"/>
-      <c r="K81" s="62"/>
-      <c r="L81" s="62"/>
-      <c r="M81" s="62"/>
-    </row>
-    <row r="82" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G82" s="62"/>
-      <c r="H82" s="62"/>
-      <c r="I82" s="62"/>
-      <c r="J82" s="62"/>
-      <c r="K82" s="62"/>
-      <c r="L82" s="62"/>
-      <c r="M82" s="62"/>
-    </row>
-    <row r="83" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G83" s="62"/>
-      <c r="H83" s="62"/>
-      <c r="I83" s="62"/>
-      <c r="J83" s="62"/>
-      <c r="K83" s="62"/>
-      <c r="L83" s="62"/>
-      <c r="M83" s="62"/>
-    </row>
-    <row r="84" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G84" s="62"/>
-      <c r="H84" s="62"/>
-      <c r="I84" s="62"/>
-      <c r="J84" s="62"/>
-      <c r="K84" s="62"/>
-      <c r="L84" s="62"/>
-      <c r="M84" s="62"/>
-    </row>
-    <row r="85" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G85" s="62"/>
-      <c r="H85" s="62"/>
-      <c r="I85" s="62"/>
-      <c r="J85" s="62"/>
-      <c r="K85" s="62"/>
-      <c r="L85" s="62"/>
-      <c r="M85" s="62"/>
-    </row>
-    <row r="86" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G86" s="62"/>
-      <c r="H86" s="62"/>
-      <c r="I86" s="62"/>
-      <c r="J86" s="62"/>
-      <c r="K86" s="62"/>
-      <c r="L86" s="62"/>
-      <c r="M86" s="62"/>
-    </row>
-    <row r="87" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G87" s="62"/>
-    </row>
-    <row r="88" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G88" s="62"/>
-    </row>
-    <row r="89" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G89" s="62"/>
-    </row>
-    <row r="90" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G90" s="62"/>
-    </row>
-    <row r="91" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G91" s="62"/>
-    </row>
-    <row r="92" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G92" s="62"/>
-    </row>
-    <row r="93" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G93" s="62"/>
-    </row>
-    <row r="94" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G94" s="62"/>
-    </row>
-    <row r="95" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G95" s="62"/>
-    </row>
-    <row r="96" spans="7:13" x14ac:dyDescent="0.25">
-      <c r="G96" s="62"/>
-    </row>
-    <row r="97" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G97" s="62"/>
-    </row>
-    <row r="98" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G98" s="62"/>
-    </row>
-    <row r="99" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G99" s="62"/>
-    </row>
-    <row r="100" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G100" s="62"/>
-    </row>
-    <row r="101" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G101" s="62"/>
+      <c r="A74" s="78"/>
+      <c r="B74" s="78"/>
+      <c r="C74" s="78"/>
+      <c r="D74" s="78"/>
+      <c r="E74" s="78"/>
+      <c r="F74" s="78"/>
+      <c r="G74" s="78"/>
+      <c r="H74" s="78"/>
+      <c r="I74" s="78"/>
+      <c r="J74" s="78"/>
+      <c r="K74" s="78"/>
+      <c r="L74" s="78"/>
+      <c r="M74" s="78"/>
+      <c r="N74" s="78"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4218,12 +3972,12 @@
   <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="217.5" style="51" customWidth="1"/>
-    <col min="2" max="16384" width="10.83203125" style="51"/>
+    <col min="1" max="1" width="217.5" style="48" customWidth="1"/>
+    <col min="2" max="16384" width="10.83203125" style="48"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="93" t="s">
         <v>147</v>
       </c>
     </row>
@@ -4233,12 +3987,12 @@
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="48" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="48" t="s">
         <v>144</v>
       </c>
     </row>
@@ -4253,27 +4007,27 @@
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="48" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="51" t="s">
+      <c r="A9" s="48" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="51" t="s">
+      <c r="A10" s="48" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="51" t="s">
+      <c r="A11" s="48" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="51" t="s">
+      <c r="A12" s="48" t="s">
         <v>150</v>
       </c>
     </row>
@@ -4283,17 +4037,17 @@
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="48" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="51" t="s">
+      <c r="A16" s="48" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="48" t="s">
         <v>152</v>
       </c>
     </row>
@@ -4303,17 +4057,17 @@
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="51" t="s">
+      <c r="A20" s="48" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="51" t="s">
+      <c r="A21" s="48" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="51" t="s">
+      <c r="A22" s="48" t="s">
         <v>153</v>
       </c>
     </row>
@@ -4323,12 +4077,12 @@
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="51" t="s">
+      <c r="A25" s="48" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="51" t="s">
+      <c r="A26" s="48" t="s">
         <v>165</v>
       </c>
     </row>
@@ -4364,20 +4118,19 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" s="5"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
-      <c r="F9" s="27"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
@@ -4386,45 +4139,45 @@
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
-      <c r="F10" s="42" cm="1" vm="1">
+      <c r="F10" s="39" cm="1" vm="1">
         <f t="array" aca="1" ref="F10" ca="1">_xlfn.TAKE(_xlfn.STOCKHISTORY("MU", TODAY()-7, TODAY()-1, 0, 0, 1), -1)</f>
-        <v>294.37</v>
+        <v>1016.59</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="F11" s="43">
+      <c r="F11" s="40">
         <v>1122.4666035</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F12" s="41"/>
+      <c r="F12" s="38"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="43">
+      <c r="F13" s="40">
         <f ca="1">F11*F10</f>
-        <v>330420.49407229503</v>
+        <v>1141088.3244520652</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="47">
+      <c r="F14" s="44">
         <f ca="1">F13/$F$25</f>
-        <v>0.9556008639692718</v>
+        <v>0.98672477976131279</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="47">
+      <c r="F15" s="44">
         <f>F16+(F17*F18)</f>
         <v>0.11862</v>
       </c>
@@ -4433,7 +4186,7 @@
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="45">
+      <c r="F16" s="42">
         <v>4.1119999999999997E-2</v>
       </c>
     </row>
@@ -4441,7 +4194,7 @@
       <c r="B17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="38">
         <v>1.55</v>
       </c>
     </row>
@@ -4449,18 +4202,18 @@
       <c r="B18" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F18" s="45">
+      <c r="F18" s="42">
         <v>0.05</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F19" s="41"/>
+      <c r="F19" s="38"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B20" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="41">
+      <c r="F20" s="38">
         <f>15352</f>
         <v>15352</v>
       </c>
@@ -4469,16 +4222,16 @@
       <c r="B21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="44">
+      <c r="F21" s="41">
         <f ca="1">F20/F25</f>
-        <v>4.4399136030728238E-2</v>
+        <v>1.3275220238687159E-2</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F22" s="47">
+      <c r="F22" s="44">
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
@@ -4486,32 +4239,32 @@
       <c r="B23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F23" s="46">
+      <c r="F23" s="43">
         <v>0.21</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F24" s="41"/>
+      <c r="F24" s="38"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B25" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F25" s="43">
+      <c r="F25" s="40">
         <f ca="1">F13+F20</f>
-        <v>345772.49407229503</v>
+        <v>1156440.3244520652</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="F26" s="41"/>
+      <c r="F26" s="38"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="45">
+      <c r="F27" s="42">
         <f ca="1">F14*F15+(F21*F22*(1-F23))</f>
-        <v>0.11496683908739169</v>
+        <v>0.11752771487876082</v>
       </c>
     </row>
   </sheetData>
@@ -4526,19 +4279,19 @@
   <cols>
     <col min="1" max="1" width="53.83203125" style="17" customWidth="1"/>
     <col min="2" max="9" width="12.83203125" style="17" customWidth="1"/>
-    <col min="10" max="15" width="10.83203125" style="34"/>
+    <col min="10" max="15" width="10.83203125" style="32"/>
     <col min="16" max="16384" width="10.83203125" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="35" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="15" cm="1" vm="1">
         <f t="array" aca="1" ref="A2" ca="1">_xlfn.TAKE(_xlfn.STOCKHISTORY("MU", TODAY()-7, TODAY()-1, 0, 0, 1), -1)</f>
-        <v>294.37</v>
+        <v>1016.59</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -4575,48 +4328,48 @@
       <c r="A5" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="29">
         <f>'Income Statement'!B26</f>
         <v>14138</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="29">
         <f>'Income Statement'!C26</f>
         <v>6358</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="29">
         <f>'Income Statement'!D26</f>
         <v>2710</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="29">
         <f>'Income Statement'!E26</f>
         <v>5861</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="29">
         <f>'Income Statement'!F26</f>
         <v>8687</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="29">
         <f>'Income Statement'!G26</f>
         <v>-5833</v>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="29">
         <f>'Income Statement'!H26</f>
         <v>778</v>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="29">
         <f>'Income Statement'!I26</f>
         <v>8539</v>
       </c>
@@ -4625,66 +4378,66 @@
       <c r="A7" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="28">
         <f>'Income Statement'!B8</f>
         <v>4759</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="28">
         <f>'Income Statement'!C8</f>
         <v>5424</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="28">
         <f>'Income Statement'!D8</f>
         <v>5650</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="28">
         <f>'Income Statement'!E8</f>
         <v>6214</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="28">
         <f>'Income Statement'!F8</f>
         <v>7116</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="28">
         <f>'Income Statement'!G8</f>
         <v>7756</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="28">
         <f>'Income Statement'!H8</f>
         <v>7780</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="28">
         <f>'Income Statement'!I8</f>
         <v>8352</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="27">
         <v>101</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="27">
         <v>49</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="27">
         <v>26</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="27">
         <v>454</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="27">
         <v>44</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="27">
         <f>1831+101</f>
         <v>1932</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="27">
         <v>0</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="27">
         <v>0</v>
       </c>
     </row>
@@ -4692,28 +4445,28 @@
       <c r="A9" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="26">
         <v>198</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="26">
         <v>243</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="26">
         <v>328</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="26">
         <v>378</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="26">
         <v>514</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="26">
         <v>596</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="26">
         <v>833</v>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="26">
         <v>972</v>
       </c>
     </row>
@@ -4721,28 +4474,28 @@
       <c r="A10" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="27">
         <v>385</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="27">
         <v>396</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="27">
         <v>-40</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="27">
         <v>1</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="27">
         <v>83</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="27">
         <v>0</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="27">
         <v>0</v>
       </c>
-      <c r="I10" s="29">
+      <c r="I10" s="27">
         <v>0</v>
       </c>
     </row>
@@ -4750,35 +4503,35 @@
       <c r="A11" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="26">
         <f>SUM(B12:B16)</f>
         <v>-2181</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="26">
         <f t="shared" ref="C11:I11" si="0">SUM(C12:C16)</f>
         <v>719</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="26">
         <f t="shared" si="0"/>
         <v>-368</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="26">
         <f t="shared" si="0"/>
         <v>-440</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="26">
         <f t="shared" si="0"/>
         <v>-1263</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="26">
         <f t="shared" si="0"/>
         <v>-2892</v>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="26">
         <f t="shared" si="0"/>
         <v>-884</v>
       </c>
-      <c r="I11" s="28">
+      <c r="I11" s="26">
         <f t="shared" si="0"/>
         <v>-338</v>
       </c>
@@ -4787,28 +4540,28 @@
       <c r="A12" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="27">
         <v>-1734</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="27">
         <v>2431</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="27">
         <v>-723</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="27">
         <v>-1446</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="27">
         <v>190</v>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="27">
         <v>2763</v>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="27">
         <v>-3581</v>
       </c>
-      <c r="I12" s="29">
+      <c r="I12" s="27">
         <v>-1776</v>
       </c>
     </row>
@@ -4816,28 +4569,28 @@
       <c r="A13" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="26">
         <v>-472</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="26">
         <v>-1528</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="26">
         <v>-489</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="26">
         <v>866</v>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="26">
         <v>-2179</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="26">
         <v>-3555</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="26">
         <v>-488</v>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="26">
         <v>520</v>
       </c>
     </row>
@@ -4845,28 +4598,28 @@
       <c r="A14" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="27">
         <v>668</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="27">
         <v>-174</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="27">
         <v>725</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="27">
         <v>210</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="27">
         <v>744</v>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="27">
         <v>-1302</v>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="27">
         <v>1915</v>
       </c>
-      <c r="I14" s="29">
+      <c r="I14" s="27">
         <v>862</v>
       </c>
     </row>
@@ -4874,60 +4627,60 @@
       <c r="A15" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="26">
         <v>-378</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="26">
         <v>-160</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="26">
         <v>40</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="26">
         <v>-70</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="26">
         <v>-18</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="26">
         <f>-817+19</f>
         <v>-798</v>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="26">
         <f>989+281</f>
         <v>1270</v>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="26">
         <f>-272+328</f>
         <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="27">
         <v>-265</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="27">
         <v>150</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="27">
         <v>79</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="27">
         <v>0</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="27">
         <v>0</v>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="27">
         <v>0</v>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="27">
         <v>0</v>
       </c>
-      <c r="I16" s="29">
+      <c r="I16" s="27">
         <v>0</v>
       </c>
     </row>
@@ -4935,35 +4688,35 @@
       <c r="A17" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="28">
         <f>B6+SUM(B7:B16)</f>
         <v>15219</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="28">
         <f t="shared" ref="C17:I17" si="1">C6+SUM(C7:C16)</f>
         <v>13908</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="28">
         <f t="shared" si="1"/>
         <v>7938</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="28">
         <f t="shared" si="1"/>
         <v>12028</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="28">
         <f t="shared" si="1"/>
         <v>13918</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="28">
         <f t="shared" si="1"/>
         <v>-1333</v>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="28">
         <f t="shared" si="1"/>
         <v>7623</v>
       </c>
-      <c r="I17" s="30">
+      <c r="I17" s="28">
         <f t="shared" si="1"/>
         <v>17187</v>
       </c>
@@ -4972,41 +4725,41 @@
       <c r="A18" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="28">
         <v>-8879</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="28">
         <v>-9780</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="28">
         <v>-8223</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="28">
         <v>-10030</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="28">
         <v>-12067</v>
       </c>
-      <c r="G19" s="30">
+      <c r="G19" s="28">
         <v>-7676</v>
       </c>
-      <c r="H19" s="30">
+      <c r="H19" s="28">
         <v>-8386</v>
       </c>
-      <c r="I19" s="30">
+      <c r="I19" s="28">
         <v>-15857</v>
       </c>
     </row>
@@ -5014,28 +4767,28 @@
       <c r="A20" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="27">
         <v>-760</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="27">
         <v>-4218</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="27">
         <v>-1857</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="27">
         <v>-3163</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="27">
         <v>-1770</v>
       </c>
-      <c r="G20" s="29">
+      <c r="G20" s="27">
         <v>-723</v>
       </c>
-      <c r="H20" s="29">
+      <c r="H20" s="27">
         <v>-1999</v>
       </c>
-      <c r="I20" s="29">
+      <c r="I20" s="27">
         <v>-1890</v>
       </c>
     </row>
@@ -5043,116 +4796,116 @@
       <c r="A21" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="26">
         <v>604</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="26">
         <v>1504</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="26">
         <v>1458</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="26">
         <v>856</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="26">
         <v>294</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="26">
         <v>1591</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="26">
         <v>1794</v>
       </c>
-      <c r="I21" s="28">
+      <c r="I21" s="26">
         <v>1698</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="35" t="s">
+      <c r="A22" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="27">
         <v>320</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="27">
         <v>1541</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="27">
         <v>814</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="27">
         <v>1250</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="27">
         <v>1321</v>
       </c>
-      <c r="G22" s="29">
+      <c r="G22" s="27">
         <v>0</v>
       </c>
-      <c r="H22" s="29">
+      <c r="H22" s="27">
         <v>0</v>
       </c>
-      <c r="I22" s="29">
+      <c r="I22" s="27">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="39" t="s">
+      <c r="A23" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="26">
         <v>355</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="26">
         <v>748</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="26">
         <v>262</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="26">
         <v>495</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="26">
         <v>115</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="26">
         <v>710</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="26">
         <v>315</v>
       </c>
-      <c r="I23" s="28">
+      <c r="I23" s="26">
         <v>2005</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="35" t="s">
+      <c r="A24" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="27">
         <v>144</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="27">
         <v>120</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="27">
         <v>-43</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="27">
         <v>3</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="27">
         <f>888-366</f>
         <v>522</v>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="27">
         <v>-93</v>
       </c>
-      <c r="H24" s="29">
+      <c r="H24" s="27">
         <v>-33</v>
       </c>
-      <c r="I24" s="29">
+      <c r="I24" s="27">
         <v>-43</v>
       </c>
     </row>
@@ -5160,35 +4913,35 @@
       <c r="A25" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="26">
         <f>B22+B21</f>
         <v>924</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="26">
         <f t="shared" ref="C25:I25" si="2">C22+C21</f>
         <v>3045</v>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="26">
         <f t="shared" si="2"/>
         <v>2272</v>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="26">
         <f t="shared" si="2"/>
         <v>2106</v>
       </c>
-      <c r="F25" s="28">
+      <c r="F25" s="26">
         <f t="shared" si="2"/>
         <v>1615</v>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="26">
         <f t="shared" si="2"/>
         <v>1591</v>
       </c>
-      <c r="H25" s="28">
+      <c r="H25" s="26">
         <f t="shared" si="2"/>
         <v>1794</v>
       </c>
-      <c r="I25" s="28">
+      <c r="I25" s="26">
         <f t="shared" si="2"/>
         <v>1698</v>
       </c>
@@ -5197,35 +4950,35 @@
       <c r="A26" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="29">
         <f>SUM(B19:B24)</f>
         <v>-8216</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="29">
         <f t="shared" ref="C26:I26" si="3">SUM(C19:C24)</f>
         <v>-10085</v>
       </c>
-      <c r="D26" s="31">
+      <c r="D26" s="29">
         <f t="shared" si="3"/>
         <v>-7589</v>
       </c>
-      <c r="E26" s="31">
+      <c r="E26" s="29">
         <f t="shared" si="3"/>
         <v>-10589</v>
       </c>
-      <c r="F26" s="31">
+      <c r="F26" s="29">
         <f>SUM(F19:F24)</f>
         <v>-11585</v>
       </c>
-      <c r="G26" s="31">
+      <c r="G26" s="29">
         <f t="shared" si="3"/>
         <v>-6191</v>
       </c>
-      <c r="H26" s="31">
+      <c r="H26" s="29">
         <f t="shared" si="3"/>
         <v>-8309</v>
       </c>
-      <c r="I26" s="31">
+      <c r="I26" s="29">
         <f t="shared" si="3"/>
         <v>-14087</v>
       </c>
@@ -5234,41 +4987,41 @@
       <c r="A27" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B28" s="29">
+      <c r="B28" s="27">
         <v>-10194</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="27">
         <v>-3340</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="27">
         <v>-4366</v>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="27">
         <v>-1520</v>
       </c>
-      <c r="F28" s="29">
+      <c r="F28" s="27">
         <v>-2032</v>
       </c>
-      <c r="G28" s="29">
+      <c r="G28" s="27">
         <v>-761</v>
       </c>
-      <c r="H28" s="29">
+      <c r="H28" s="27">
         <v>-1897</v>
       </c>
-      <c r="I28" s="29">
+      <c r="I28" s="27">
         <v>-4619</v>
       </c>
     </row>
@@ -5276,28 +5029,28 @@
       <c r="A29" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="26">
         <v>0</v>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="26">
         <v>0</v>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="26">
         <v>-744</v>
       </c>
-      <c r="E29" s="28">
+      <c r="E29" s="26">
         <v>0</v>
       </c>
-      <c r="F29" s="28">
+      <c r="F29" s="26">
         <v>0</v>
       </c>
-      <c r="G29" s="28">
+      <c r="G29" s="26">
         <v>0</v>
       </c>
-      <c r="H29" s="28">
+      <c r="H29" s="26">
         <v>0</v>
       </c>
-      <c r="I29" s="28">
+      <c r="I29" s="26">
         <v>0</v>
       </c>
     </row>
@@ -5305,28 +5058,28 @@
       <c r="A30" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B30" s="29">
+      <c r="B30" s="27">
         <v>-71</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C30" s="27">
         <v>-2729</v>
       </c>
-      <c r="D30" s="29">
+      <c r="D30" s="27">
         <v>-251</v>
       </c>
-      <c r="E30" s="29">
+      <c r="E30" s="27">
         <v>-1200</v>
       </c>
-      <c r="F30" s="29">
+      <c r="F30" s="27">
         <v>-2432</v>
       </c>
-      <c r="G30" s="29">
+      <c r="G30" s="27">
         <v>-425</v>
       </c>
-      <c r="H30" s="29">
+      <c r="H30" s="27">
         <v>-300</v>
       </c>
-      <c r="I30" s="29">
+      <c r="I30" s="27">
         <v>0</v>
       </c>
     </row>
@@ -5334,28 +5087,28 @@
       <c r="A31" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="26">
         <v>0</v>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="26">
         <v>0</v>
       </c>
-      <c r="D31" s="28">
+      <c r="D31" s="26">
         <v>0</v>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="26">
         <v>0</v>
       </c>
-      <c r="F31" s="28">
+      <c r="F31" s="26">
         <v>-461</v>
       </c>
-      <c r="G31" s="28">
+      <c r="G31" s="26">
         <v>-504</v>
       </c>
-      <c r="H31" s="28">
+      <c r="H31" s="26">
         <v>-513</v>
       </c>
-      <c r="I31" s="28">
+      <c r="I31" s="26">
         <v>-522</v>
       </c>
     </row>
@@ -5363,57 +5116,57 @@
       <c r="A32" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="27">
         <v>-206</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="27">
         <v>-75</v>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="27">
         <v>-63</v>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="27">
         <v>-295</v>
       </c>
-      <c r="F32" s="29">
+      <c r="F32" s="27">
         <v>-141</v>
       </c>
-      <c r="G32" s="29">
+      <c r="G32" s="27">
         <v>-138</v>
       </c>
-      <c r="H32" s="29">
+      <c r="H32" s="27">
         <v>-149</v>
       </c>
-      <c r="I32" s="29">
+      <c r="I32" s="27">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33" s="33" t="s">
+      <c r="A33" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="26">
         <v>1009</v>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="26">
         <v>3550</v>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="26">
         <v>5000</v>
       </c>
-      <c r="E33" s="28">
+      <c r="E33" s="26">
         <v>1188</v>
       </c>
-      <c r="F33" s="28">
+      <c r="F33" s="26">
         <v>2000</v>
       </c>
-      <c r="G33" s="28">
+      <c r="G33" s="26">
         <v>6716</v>
       </c>
-      <c r="H33" s="28">
+      <c r="H33" s="26">
         <v>999</v>
       </c>
-      <c r="I33" s="28">
+      <c r="I33" s="26">
         <v>4430</v>
       </c>
     </row>
@@ -5421,28 +5174,28 @@
       <c r="A34" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B34" s="29">
+      <c r="B34" s="27">
         <v>1655</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C34" s="27">
         <v>179</v>
       </c>
-      <c r="D34" s="29">
+      <c r="D34" s="27">
         <v>225</v>
       </c>
-      <c r="E34" s="29">
+      <c r="E34" s="27">
         <v>140</v>
       </c>
-      <c r="F34" s="29">
+      <c r="F34" s="27">
         <v>211</v>
       </c>
-      <c r="G34" s="29">
+      <c r="G34" s="27">
         <v>0</v>
       </c>
-      <c r="H34" s="29">
+      <c r="H34" s="27">
         <v>0</v>
       </c>
-      <c r="I34" s="29">
+      <c r="I34" s="27">
         <v>0</v>
       </c>
     </row>
@@ -5450,30 +5203,30 @@
       <c r="A35" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="B35" s="28">
+      <c r="B35" s="26">
         <v>31</v>
       </c>
-      <c r="C35" s="28">
+      <c r="C35" s="26">
         <v>-23</v>
       </c>
-      <c r="D35" s="28">
+      <c r="D35" s="26">
         <v>-118</v>
       </c>
-      <c r="E35" s="28">
+      <c r="E35" s="26">
         <f>140-94</f>
         <v>46</v>
       </c>
-      <c r="F35" s="28">
+      <c r="F35" s="26">
         <f>211-125</f>
         <v>86</v>
       </c>
-      <c r="G35" s="28">
+      <c r="G35" s="26">
         <v>95</v>
       </c>
-      <c r="H35" s="28">
+      <c r="H35" s="26">
         <v>18</v>
       </c>
-      <c r="I35" s="28">
+      <c r="I35" s="26">
         <v>-139</v>
       </c>
     </row>
@@ -5481,35 +5234,35 @@
       <c r="A36" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="31">
+      <c r="B36" s="29">
         <f>SUM(B28:B35)</f>
         <v>-7776</v>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="29">
         <f t="shared" ref="C36:I36" si="4">SUM(C28:C35)</f>
         <v>-2438</v>
       </c>
-      <c r="D36" s="31">
+      <c r="D36" s="29">
         <f t="shared" si="4"/>
         <v>-317</v>
       </c>
-      <c r="E36" s="31">
+      <c r="E36" s="29">
         <f>SUM(E28:E35)-E34</f>
         <v>-1781</v>
       </c>
-      <c r="F36" s="31">
+      <c r="F36" s="29">
         <f>SUM(F28:F35)-F34</f>
         <v>-2980</v>
       </c>
-      <c r="G36" s="31">
+      <c r="G36" s="29">
         <f t="shared" si="4"/>
         <v>4983</v>
       </c>
-      <c r="H36" s="31">
+      <c r="H36" s="29">
         <f t="shared" si="4"/>
         <v>-1842</v>
       </c>
-      <c r="I36" s="31">
+      <c r="I36" s="29">
         <f t="shared" si="4"/>
         <v>-850</v>
       </c>
@@ -5518,41 +5271,41 @@
       <c r="A37" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="29">
+      <c r="B38" s="27">
         <v>-37</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="27">
         <v>26</v>
       </c>
-      <c r="D38" s="29">
+      <c r="D38" s="27">
         <v>11</v>
       </c>
-      <c r="E38" s="29">
+      <c r="E38" s="27">
         <v>41</v>
       </c>
-      <c r="F38" s="29">
+      <c r="F38" s="27">
         <v>-106</v>
       </c>
-      <c r="G38" s="29">
+      <c r="G38" s="27">
         <v>-34</v>
       </c>
-      <c r="H38" s="29">
+      <c r="H38" s="27">
         <v>40</v>
       </c>
-      <c r="I38" s="29">
+      <c r="I38" s="27">
         <v>6</v>
       </c>
     </row>
@@ -5560,35 +5313,35 @@
       <c r="A39" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="B39" s="28">
+      <c r="B39" s="26">
         <f>B17+B26+B36+B38</f>
         <v>-810</v>
       </c>
-      <c r="C39" s="28">
+      <c r="C39" s="26">
         <f t="shared" ref="C39:I39" si="5">C17+C26+C36+C38</f>
         <v>1411</v>
       </c>
-      <c r="D39" s="28">
+      <c r="D39" s="26">
         <f t="shared" si="5"/>
         <v>43</v>
       </c>
-      <c r="E39" s="28">
+      <c r="E39" s="26">
         <f t="shared" si="5"/>
         <v>-301</v>
       </c>
-      <c r="F39" s="28">
+      <c r="F39" s="26">
         <f t="shared" si="5"/>
         <v>-753</v>
       </c>
-      <c r="G39" s="28">
+      <c r="G39" s="26">
         <f t="shared" si="5"/>
         <v>-2575</v>
       </c>
-      <c r="H39" s="28">
+      <c r="H39" s="26">
         <f t="shared" si="5"/>
         <v>-2488</v>
       </c>
-      <c r="I39" s="28">
+      <c r="I39" s="26">
         <f t="shared" si="5"/>
         <v>2256</v>
       </c>
@@ -5597,35 +5350,35 @@
       <c r="A40" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B40" s="31">
+      <c r="B40" s="29">
         <f>B17+B19</f>
         <v>6340</v>
       </c>
-      <c r="C40" s="31">
+      <c r="C40" s="29">
         <f t="shared" ref="C40:I40" si="6">C17+C19</f>
         <v>4128</v>
       </c>
-      <c r="D40" s="31">
+      <c r="D40" s="29">
         <f t="shared" si="6"/>
         <v>-285</v>
       </c>
-      <c r="E40" s="31">
+      <c r="E40" s="29">
         <f t="shared" si="6"/>
         <v>1998</v>
       </c>
-      <c r="F40" s="31">
+      <c r="F40" s="29">
         <f t="shared" si="6"/>
         <v>1851</v>
       </c>
-      <c r="G40" s="31">
+      <c r="G40" s="29">
         <f t="shared" si="6"/>
         <v>-9009</v>
       </c>
-      <c r="H40" s="31">
+      <c r="H40" s="29">
         <f t="shared" si="6"/>
         <v>-763</v>
       </c>
-      <c r="I40" s="31">
+      <c r="I40" s="29">
         <f t="shared" si="6"/>
         <v>1330</v>
       </c>
@@ -5634,35 +5387,35 @@
       <c r="A41" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="B41" s="40">
+      <c r="B41" s="37">
         <f>B40/'Income Statement'!B30</f>
         <v>5.5034722222222223</v>
       </c>
-      <c r="C41" s="40">
+      <c r="C41" s="37">
         <f>C40/'Income Statement'!C30</f>
         <v>3.7055655296229801</v>
       </c>
-      <c r="D41" s="40">
+      <c r="D41" s="37">
         <f>D40/'Income Statement'!D30</f>
         <v>-0.25675675675675674</v>
       </c>
-      <c r="E41" s="40">
+      <c r="E41" s="37">
         <f>E40/'Income Statement'!E30</f>
         <v>1.7839285714285715</v>
       </c>
-      <c r="F41" s="40">
+      <c r="F41" s="37">
         <f>F40/'Income Statement'!F30</f>
         <v>1.664568345323741</v>
       </c>
-      <c r="G41" s="40">
+      <c r="G41" s="37">
         <f>G40/'Income Statement'!G30</f>
         <v>-8.2424519670631291</v>
       </c>
-      <c r="H41" s="40">
+      <c r="H41" s="37">
         <f>H40/'Income Statement'!H30</f>
         <v>-0.69049773755656108</v>
       </c>
-      <c r="I41" s="40">
+      <c r="I41" s="37">
         <f>I40/'Income Statement'!I30</f>
         <v>1.1917562724014337</v>
       </c>
@@ -5671,41 +5424,41 @@
       <c r="A42" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B42" s="37">
+      <c r="B42" s="34">
         <f ca="1">(B41/A2)</f>
-        <v>1.8695764589537731E-2</v>
-      </c>
-      <c r="C42" s="37">
+        <v>5.4136596093038707E-3</v>
+      </c>
+      <c r="C42" s="34">
         <f ca="1">(C41/A2)</f>
-        <v>1.2588122191877502E-2</v>
-      </c>
-      <c r="D42" s="37">
+        <v>3.645093429625493E-3</v>
+      </c>
+      <c r="D42" s="34">
         <f ca="1">(D41/A2)</f>
-        <v>-8.7222460426251568E-4</v>
-      </c>
-      <c r="E42" s="37">
+        <v>-2.5256667560841315E-4</v>
+      </c>
+      <c r="E42" s="34">
         <f ca="1">(E41/A2)</f>
-        <v>6.0601575276983781E-3</v>
-      </c>
-      <c r="F42" s="37">
+        <v>1.7548161711492061E-3</v>
+      </c>
+      <c r="F42" s="34">
         <f ca="1">(F41/A2)</f>
-        <v>5.6546806580960729E-3</v>
-      </c>
-      <c r="G42" s="37">
+        <v>1.6374038160160349E-3</v>
+      </c>
+      <c r="G42" s="34">
         <f ca="1">(G41/A2)</f>
-        <v>-2.8000312419958314E-2</v>
-      </c>
-      <c r="H42" s="37">
+        <v>-8.1079412221870453E-3</v>
+      </c>
+      <c r="H42" s="34">
         <f ca="1">(H41/A2)</f>
-        <v>-2.3456797144972689E-3</v>
-      </c>
-      <c r="I42" s="37">
+        <v>-6.7922932308655507E-4</v>
+      </c>
+      <c r="I42" s="34">
         <f ca="1">(I41/A2)</f>
-        <v>4.0484977151252965E-3</v>
+        <v>1.172307687859839E-3</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" s="32" t="s">
+      <c r="A43" s="30" t="s">
         <v>45</v>
       </c>
       <c r="B43" s="21"/>
@@ -5744,13 +5497,13 @@
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="15" cm="1" vm="1">
         <f t="array" aca="1" ref="A2" ca="1">_xlfn.TAKE(_xlfn.STOCKHISTORY("MU", TODAY()-7, TODAY()-1, 0, 0, 1), -1)</f>
-        <v>294.37</v>
+        <v>1016.59</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="7"/>
     </row>
-    <row r="4" spans="1:9" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="18"/>
       <c r="B4" s="19" t="s">
         <v>48</v>
@@ -5781,28 +5534,28 @@
       <c r="A5" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="28">
         <v>30391</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="28">
         <v>23406</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="28">
         <v>21435</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="28">
         <v>27705</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="28">
         <v>30758</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="28">
         <v>15540</v>
       </c>
-      <c r="H5" s="30">
+      <c r="H5" s="28">
         <v>25111</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="28">
         <v>37378</v>
       </c>
     </row>
@@ -5810,28 +5563,28 @@
       <c r="A6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="29">
         <v>12500</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="29">
         <v>12704</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="29">
         <v>14883</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="29">
         <v>17282</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="29">
         <v>16860</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="29">
         <v>16956</v>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="29">
         <v>19498</v>
       </c>
-      <c r="I6" s="31">
+      <c r="I6" s="29">
         <v>22505</v>
       </c>
     </row>
@@ -5839,35 +5592,35 @@
       <c r="A7" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="26">
         <f>B6-B8</f>
         <v>7741</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="26">
         <f t="shared" ref="C7:I7" si="0">C6-C8</f>
         <v>7280</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="26">
         <f t="shared" si="0"/>
         <v>9233</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="26">
         <f t="shared" si="0"/>
         <v>11068</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="26">
         <f t="shared" si="0"/>
         <v>9744</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="26">
         <f t="shared" si="0"/>
         <v>9200</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="26">
         <f t="shared" si="0"/>
         <v>11718</v>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="26">
         <f t="shared" si="0"/>
         <v>14153</v>
       </c>
@@ -5876,28 +5629,28 @@
       <c r="A8" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="29">
         <v>4759</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="29">
         <v>5424</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="29">
         <v>5650</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="29">
         <v>6214</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="29">
         <v>7116</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="27">
         <v>7756</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="27">
         <v>7780</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="27">
         <v>8352</v>
       </c>
     </row>
@@ -5905,35 +5658,35 @@
       <c r="A9" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="28">
         <f>B5-B6</f>
         <v>17891</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="28">
         <f t="shared" ref="C9:I9" si="1">C5-C6</f>
         <v>10702</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="28">
         <f t="shared" si="1"/>
         <v>6552</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="28">
         <f t="shared" si="1"/>
         <v>10423</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="28">
         <f t="shared" si="1"/>
         <v>13898</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="28">
         <f t="shared" si="1"/>
         <v>-1416</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="28">
         <f t="shared" si="1"/>
         <v>5613</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="28">
         <f t="shared" si="1"/>
         <v>14873</v>
       </c>
@@ -5942,28 +5695,28 @@
       <c r="A10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="29">
         <v>813</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="29">
         <v>836</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="29">
         <v>881</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="29">
         <v>894</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="29">
         <v>1066</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="29">
         <v>920</v>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="29">
         <v>1129</v>
       </c>
-      <c r="I10" s="31">
+      <c r="I10" s="29">
         <v>1205</v>
       </c>
     </row>
@@ -5971,28 +5724,28 @@
       <c r="A11" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="26">
         <v>2141</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="26">
         <v>2441</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="26">
         <v>2600</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="26">
         <v>2663</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="26">
         <v>3116</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="26">
         <v>3114</v>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="26">
         <v>3430</v>
       </c>
-      <c r="I11" s="28">
+      <c r="I11" s="26">
         <v>3798</v>
       </c>
     </row>
@@ -6000,28 +5753,28 @@
       <c r="A12" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="27">
         <v>-57</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="27">
         <v>49</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="27">
         <v>68</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="27">
         <v>95</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="27">
         <v>-34</v>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="27">
         <v>124</v>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="27">
         <v>-251</v>
       </c>
-      <c r="I12" s="29">
+      <c r="I12" s="27">
         <v>61</v>
       </c>
     </row>
@@ -6029,35 +5782,35 @@
       <c r="A13" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="28">
         <f>B5-B6-SUM(B10:B12)-B19</f>
         <v>14994</v>
       </c>
-      <c r="C13" s="30">
-        <f t="shared" ref="C13:I13" si="2">C5-C6-SUM(C10:C12)-C19</f>
+      <c r="C13" s="28">
+        <f t="shared" ref="C13:H13" si="2">C5-C6-SUM(C10:C12)-C19</f>
         <v>7376</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="28">
         <f t="shared" si="2"/>
         <v>3003</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="28">
         <f t="shared" si="2"/>
         <v>6283</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="28">
         <f t="shared" si="2"/>
         <v>9702</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="28">
         <f t="shared" si="2"/>
         <v>-5745</v>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="28">
         <f t="shared" si="2"/>
         <v>1304</v>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="28">
         <f>I5-I6-SUM(I10:I12)-I19</f>
         <v>9770</v>
       </c>
@@ -6066,35 +5819,35 @@
       <c r="A14" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="29">
         <f>B15-B17+B16</f>
         <v>-687</v>
       </c>
-      <c r="C14" s="31">
-        <f t="shared" ref="C14:I14" si="3">C15-C17+C16</f>
+      <c r="C14" s="29">
+        <f t="shared" ref="C14:F14" si="3">C15-C17+C16</f>
         <v>-328</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="29">
         <f t="shared" si="3"/>
         <v>-20</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="29">
         <f>E15-E17+E16</f>
         <v>-65</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="29">
         <f t="shared" si="3"/>
         <v>-131</v>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="29">
         <f t="shared" ref="G14" si="4">G15-G17+G16</f>
         <v>87</v>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="29">
         <f t="shared" ref="H14" si="5">H15-H17+H16</f>
         <v>-64</v>
       </c>
-      <c r="I14" s="31">
+      <c r="I14" s="29">
         <f t="shared" ref="I14" si="6">I15-I17+I16</f>
         <v>-116</v>
       </c>
@@ -6103,28 +5856,28 @@
       <c r="A15" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="26">
         <v>120</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="26">
         <v>205</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="26">
         <v>114</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="26">
         <v>37</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="26">
         <v>96</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="26">
         <v>468</v>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="26">
         <v>529</v>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="26">
         <v>496</v>
       </c>
     </row>
@@ -6132,28 +5885,28 @@
       <c r="A16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="27">
         <v>-465</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="27">
         <v>-405</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="27">
         <v>60</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="27">
         <v>81</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="27">
         <v>-38</v>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="27">
         <v>7</v>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="27">
         <v>-31</v>
       </c>
-      <c r="I16" s="29">
+      <c r="I16" s="27">
         <v>-135</v>
       </c>
     </row>
@@ -6161,28 +5914,28 @@
       <c r="A17" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="28">
         <v>342</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="28">
         <v>128</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="28">
         <v>194</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="28">
         <v>183</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="28">
         <v>189</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="28">
         <v>388</v>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="28">
         <v>562</v>
       </c>
-      <c r="I17" s="30">
+      <c r="I17" s="28">
         <v>477</v>
       </c>
     </row>
@@ -6190,35 +5943,35 @@
       <c r="A18" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="27">
         <f>B17-B15</f>
         <v>222</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="27">
         <f t="shared" ref="C18:I18" si="7">C17-C15</f>
         <v>-77</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="27">
         <f t="shared" si="7"/>
         <v>80</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="27">
         <f t="shared" si="7"/>
         <v>146</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="27">
         <f t="shared" si="7"/>
         <v>93</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="27">
         <f t="shared" si="7"/>
         <v>-80</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="27">
         <f t="shared" si="7"/>
         <v>33</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="27">
         <f t="shared" si="7"/>
         <v>-19</v>
       </c>
@@ -6227,28 +5980,28 @@
       <c r="A19" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="26">
         <v>0</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="26">
         <v>0</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="26">
         <v>0</v>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="26">
         <v>488</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="26">
         <v>48</v>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="26">
         <v>171</v>
       </c>
-      <c r="H19" s="28">
+      <c r="H19" s="26">
         <v>1</v>
       </c>
-      <c r="I19" s="28">
+      <c r="I19" s="26">
         <v>39</v>
       </c>
     </row>
@@ -6256,33 +6009,33 @@
       <c r="A20" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="31">
+      <c r="B20" s="29">
         <f>B21+B22</f>
         <v>-17</v>
       </c>
-      <c r="C20" s="31">
-        <f t="shared" ref="C20:I20" si="8">C21+C22</f>
+      <c r="C20" s="29">
+        <f t="shared" ref="C20:F20" si="8">C21+C22</f>
         <v>6</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="29">
         <f t="shared" si="8"/>
         <v>47</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="29">
         <f t="shared" si="8"/>
         <v>-74</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="29">
         <f t="shared" si="8"/>
         <v>-564</v>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="29">
         <v>6</v>
       </c>
-      <c r="H20" s="31">
+      <c r="H20" s="29">
         <v>33</v>
       </c>
-      <c r="I20" s="31">
+      <c r="I20" s="29">
         <v>4</v>
       </c>
     </row>
@@ -6290,28 +6043,28 @@
       <c r="A21" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="26">
         <v>-2</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="26">
         <v>9</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="26">
         <v>1</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="26">
         <v>-7</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="26">
         <v>-48</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="26">
         <v>234</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="26">
         <v>142</v>
       </c>
-      <c r="I21" s="28">
+      <c r="I21" s="26">
         <v>92</v>
       </c>
     </row>
@@ -6319,28 +6072,28 @@
       <c r="A22" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="27">
         <v>-15</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="27">
         <v>-3</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="27">
         <v>46</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="27">
         <v>-67</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="27">
         <v>-516</v>
       </c>
-      <c r="G22" s="29">
+      <c r="G22" s="27">
         <v>234</v>
       </c>
-      <c r="H22" s="29">
+      <c r="H22" s="27">
         <v>142</v>
       </c>
-      <c r="I22" s="29">
+      <c r="I22" s="27">
         <v>92</v>
       </c>
     </row>
@@ -6348,36 +6101,36 @@
       <c r="A23" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="30">
-        <f>B13+B14</f>
+      <c r="B23" s="28">
+        <f t="shared" ref="B23:I23" si="9">B13+B14</f>
         <v>14307</v>
       </c>
-      <c r="C23" s="30">
-        <f>C13+C14</f>
+      <c r="C23" s="28">
+        <f t="shared" si="9"/>
         <v>7048</v>
       </c>
-      <c r="D23" s="30">
-        <f>D13+D14</f>
+      <c r="D23" s="28">
+        <f t="shared" si="9"/>
         <v>2983</v>
       </c>
-      <c r="E23" s="30">
-        <f>E13+E14</f>
+      <c r="E23" s="28">
+        <f t="shared" si="9"/>
         <v>6218</v>
       </c>
-      <c r="F23" s="30">
-        <f>F13+F14</f>
+      <c r="F23" s="28">
+        <f t="shared" si="9"/>
         <v>9571</v>
       </c>
-      <c r="G23" s="30">
-        <f>G13+G14</f>
+      <c r="G23" s="28">
+        <f t="shared" si="9"/>
         <v>-5658</v>
       </c>
-      <c r="H23" s="30">
-        <f>H13+H14</f>
+      <c r="H23" s="28">
+        <f t="shared" si="9"/>
         <v>1240</v>
       </c>
-      <c r="I23" s="30">
-        <f>I13+I14</f>
+      <c r="I23" s="28">
+        <f t="shared" si="9"/>
         <v>9654</v>
       </c>
     </row>
@@ -6385,28 +6138,28 @@
       <c r="A24" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="29">
         <v>-168</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="29">
         <v>-693</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="29">
         <v>-280</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="29">
         <v>-394</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="29">
         <v>-888</v>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="29">
         <v>-177</v>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="29">
         <v>-451</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="29">
         <v>-1124</v>
       </c>
     </row>
@@ -6414,28 +6167,28 @@
       <c r="A25" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="26">
         <v>-1</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="26">
         <v>3</v>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="26">
         <v>7</v>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="26">
         <v>37</v>
       </c>
-      <c r="F25" s="28">
+      <c r="F25" s="26">
         <v>4</v>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="26">
         <v>2</v>
       </c>
-      <c r="H25" s="28">
+      <c r="H25" s="26">
         <v>-11</v>
       </c>
-      <c r="I25" s="28">
+      <c r="I25" s="26">
         <v>9</v>
       </c>
     </row>
@@ -6443,36 +6196,36 @@
       <c r="A26" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="29">
         <f>B25+B23+B24</f>
         <v>14138</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="29">
         <f>C25+C23+C24</f>
         <v>6358</v>
       </c>
-      <c r="D26" s="31">
-        <f t="shared" ref="C26:I27" si="9">D25+D23+D24</f>
+      <c r="D26" s="29">
+        <f t="shared" ref="D26:I26" si="10">D25+D23+D24</f>
         <v>2710</v>
       </c>
-      <c r="E26" s="31">
-        <f t="shared" si="9"/>
+      <c r="E26" s="29">
+        <f t="shared" si="10"/>
         <v>5861</v>
       </c>
-      <c r="F26" s="31">
-        <f t="shared" si="9"/>
+      <c r="F26" s="29">
+        <f t="shared" si="10"/>
         <v>8687</v>
       </c>
-      <c r="G26" s="29">
-        <f t="shared" si="9"/>
+      <c r="G26" s="27">
+        <f t="shared" si="10"/>
         <v>-5833</v>
       </c>
-      <c r="H26" s="29">
+      <c r="H26" s="27">
         <f>H25+H23+H24</f>
         <v>778</v>
       </c>
-      <c r="I26" s="29">
-        <f t="shared" si="9"/>
+      <c r="I26" s="27">
+        <f t="shared" si="10"/>
         <v>8539</v>
       </c>
     </row>
@@ -6480,30 +6233,30 @@
       <c r="A27" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="26">
         <v>14135</v>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="26">
         <v>6313</v>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="26">
         <v>2687</v>
       </c>
-      <c r="E27" s="28">
+      <c r="E27" s="26">
         <v>5861</v>
       </c>
-      <c r="F27" s="28">
+      <c r="F27" s="26">
         <v>8687</v>
       </c>
-      <c r="G27" s="28">
+      <c r="G27" s="26">
         <f>G26</f>
         <v>-5833</v>
       </c>
-      <c r="H27" s="28">
+      <c r="H27" s="26">
         <f>H26</f>
         <v>778</v>
       </c>
-      <c r="I27" s="28">
+      <c r="I27" s="26">
         <f>I26</f>
         <v>8539</v>
       </c>
@@ -6512,49 +6265,49 @@
       <c r="A28" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="30">
-        <f>B27/B30</f>
+      <c r="B29" s="28">
+        <f t="shared" ref="B29:I29" si="11">B27/B30</f>
         <v>12.269965277777779</v>
       </c>
-      <c r="C29" s="30">
-        <f>C27/C30</f>
+      <c r="C29" s="28">
+        <f t="shared" si="11"/>
         <v>5.6669658886894076</v>
       </c>
-      <c r="D29" s="30">
-        <f>D27/D30</f>
+      <c r="D29" s="28">
+        <f t="shared" si="11"/>
         <v>2.4207207207207206</v>
       </c>
-      <c r="E29" s="30">
-        <f>E27/E30</f>
+      <c r="E29" s="28">
+        <f t="shared" si="11"/>
         <v>5.2330357142857142</v>
       </c>
-      <c r="F29" s="30">
-        <f>F27/F30</f>
+      <c r="F29" s="28">
+        <f t="shared" si="11"/>
         <v>7.8120503597122299</v>
       </c>
-      <c r="G29" s="30">
-        <f>G27/G30</f>
+      <c r="G29" s="28">
+        <f t="shared" si="11"/>
         <v>-5.3366880146386091</v>
       </c>
-      <c r="H29" s="30">
-        <f>H27/H30</f>
+      <c r="H29" s="28">
+        <f t="shared" si="11"/>
         <v>0.7040723981900453</v>
       </c>
-      <c r="I29" s="30">
-        <f>I27/I30</f>
+      <c r="I29" s="28">
+        <f t="shared" si="11"/>
         <v>7.6514336917562726</v>
       </c>
     </row>
@@ -6562,28 +6315,28 @@
       <c r="A30" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="29">
+      <c r="B30" s="27">
         <v>1152</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C30" s="27">
         <v>1114</v>
       </c>
-      <c r="D30" s="29">
+      <c r="D30" s="27">
         <v>1110</v>
       </c>
-      <c r="E30" s="29">
+      <c r="E30" s="27">
         <v>1120</v>
       </c>
-      <c r="F30" s="29">
+      <c r="F30" s="27">
         <v>1112</v>
       </c>
-      <c r="G30" s="29">
+      <c r="G30" s="27">
         <v>1093</v>
       </c>
-      <c r="H30" s="29">
+      <c r="H30" s="27">
         <v>1105</v>
       </c>
-      <c r="I30" s="29">
+      <c r="I30" s="27">
         <v>1116</v>
       </c>
     </row>
@@ -6591,36 +6344,36 @@
       <c r="A31" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="30">
-        <f>B27/B32</f>
+      <c r="B31" s="28">
+        <f t="shared" ref="B31:I31" si="12">B27/B32</f>
         <v>11.501220504475183</v>
       </c>
-      <c r="C31" s="30">
-        <f>C27/C32</f>
+      <c r="C31" s="28">
+        <f t="shared" si="12"/>
         <v>5.5231846019247595</v>
       </c>
-      <c r="D31" s="30">
-        <f>D27/D32</f>
+      <c r="D31" s="28">
+        <f t="shared" si="12"/>
         <v>2.3757736516357206</v>
       </c>
-      <c r="E31" s="30">
-        <f>E27/E32</f>
+      <c r="E31" s="28">
+        <f t="shared" si="12"/>
         <v>5.1367221735319895</v>
       </c>
-      <c r="F31" s="30">
-        <f>F27/F32</f>
+      <c r="F31" s="28">
+        <f t="shared" si="12"/>
         <v>7.7424242424242422</v>
       </c>
-      <c r="G31" s="30">
-        <f>G27/G32</f>
+      <c r="G31" s="28">
+        <f t="shared" si="12"/>
         <v>-5.3366880146386091</v>
       </c>
-      <c r="H31" s="30">
-        <f>H27/H32</f>
+      <c r="H31" s="28">
+        <f t="shared" si="12"/>
         <v>0.69588550983899822</v>
       </c>
-      <c r="I31" s="30">
-        <f>I27/I32</f>
+      <c r="I31" s="28">
+        <f t="shared" si="12"/>
         <v>7.5902222222222226</v>
       </c>
     </row>
@@ -6628,28 +6381,28 @@
       <c r="A32" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="27">
         <v>1229</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="27">
         <v>1143</v>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="27">
         <v>1131</v>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="27">
         <v>1141</v>
       </c>
-      <c r="F32" s="29">
+      <c r="F32" s="27">
         <v>1122</v>
       </c>
-      <c r="G32" s="29">
+      <c r="G32" s="27">
         <v>1093</v>
       </c>
-      <c r="H32" s="29">
+      <c r="H32" s="27">
         <v>1118</v>
       </c>
-      <c r="I32" s="29">
+      <c r="I32" s="27">
         <v>1125</v>
       </c>
     </row>
@@ -6657,49 +6410,49 @@
       <c r="A33" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="31">
+      <c r="B34" s="29">
         <f>B35+B36</f>
         <v>19753</v>
       </c>
-      <c r="C34" s="31">
-        <f t="shared" ref="C34:I34" si="10">C35+C36</f>
+      <c r="C34" s="29">
+        <f t="shared" ref="C34:I34" si="13">C35+C36</f>
         <v>12800</v>
       </c>
-      <c r="D34" s="31">
-        <f t="shared" si="10"/>
+      <c r="D34" s="29">
+        <f t="shared" si="13"/>
         <v>8653</v>
       </c>
-      <c r="E34" s="31">
-        <f t="shared" si="10"/>
+      <c r="E34" s="29">
+        <f t="shared" si="13"/>
         <v>12497</v>
       </c>
-      <c r="F34" s="31">
-        <f t="shared" si="10"/>
+      <c r="F34" s="29">
+        <f t="shared" si="13"/>
         <v>16818</v>
       </c>
-      <c r="G34" s="31">
-        <f t="shared" si="10"/>
+      <c r="G34" s="29">
+        <f t="shared" si="13"/>
         <v>2011</v>
       </c>
-      <c r="H34" s="31">
-        <f t="shared" si="10"/>
+      <c r="H34" s="29">
+        <f t="shared" si="13"/>
         <v>9084</v>
       </c>
-      <c r="I34" s="31">
-        <f t="shared" si="10"/>
+      <c r="I34" s="29">
+        <f t="shared" si="13"/>
         <v>18122</v>
       </c>
     </row>
@@ -6707,36 +6460,36 @@
       <c r="A35" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="28">
+      <c r="B35" s="26">
         <f>B13</f>
         <v>14994</v>
       </c>
-      <c r="C35" s="28">
-        <f t="shared" ref="C35:I35" si="11">C13</f>
+      <c r="C35" s="26">
+        <f t="shared" ref="C35:I35" si="14">C13</f>
         <v>7376</v>
       </c>
-      <c r="D35" s="28">
-        <f t="shared" si="11"/>
+      <c r="D35" s="26">
+        <f t="shared" si="14"/>
         <v>3003</v>
       </c>
-      <c r="E35" s="28">
-        <f t="shared" si="11"/>
+      <c r="E35" s="26">
+        <f t="shared" si="14"/>
         <v>6283</v>
       </c>
-      <c r="F35" s="28">
-        <f t="shared" si="11"/>
+      <c r="F35" s="26">
+        <f t="shared" si="14"/>
         <v>9702</v>
       </c>
-      <c r="G35" s="28">
-        <f t="shared" si="11"/>
+      <c r="G35" s="26">
+        <f t="shared" si="14"/>
         <v>-5745</v>
       </c>
-      <c r="H35" s="28">
-        <f t="shared" si="11"/>
+      <c r="H35" s="26">
+        <f t="shared" si="14"/>
         <v>1304</v>
       </c>
-      <c r="I35" s="28">
-        <f t="shared" si="11"/>
+      <c r="I35" s="26">
+        <f t="shared" si="14"/>
         <v>9770</v>
       </c>
     </row>
@@ -6744,41 +6497,41 @@
       <c r="A36" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B36" s="29">
+      <c r="B36" s="27">
         <f>B8</f>
         <v>4759</v>
       </c>
-      <c r="C36" s="29">
-        <f t="shared" ref="C36:I36" si="12">C8</f>
+      <c r="C36" s="27">
+        <f t="shared" ref="C36:I36" si="15">C8</f>
         <v>5424</v>
       </c>
-      <c r="D36" s="29">
-        <f t="shared" si="12"/>
+      <c r="D36" s="27">
+        <f t="shared" si="15"/>
         <v>5650</v>
       </c>
-      <c r="E36" s="29">
-        <f t="shared" si="12"/>
+      <c r="E36" s="27">
+        <f t="shared" si="15"/>
         <v>6214</v>
       </c>
-      <c r="F36" s="29">
-        <f t="shared" si="12"/>
+      <c r="F36" s="27">
+        <f t="shared" si="15"/>
         <v>7116</v>
       </c>
-      <c r="G36" s="29">
-        <f t="shared" si="12"/>
+      <c r="G36" s="27">
+        <f t="shared" si="15"/>
         <v>7756</v>
       </c>
-      <c r="H36" s="29">
-        <f t="shared" si="12"/>
+      <c r="H36" s="27">
+        <f t="shared" si="15"/>
         <v>7780</v>
       </c>
-      <c r="I36" s="29">
-        <f t="shared" si="12"/>
+      <c r="I36" s="27">
+        <f t="shared" si="15"/>
         <v>8352</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A37" s="32" t="s">
+      <c r="A37" s="30" t="s">
         <v>45</v>
       </c>
       <c r="B37" s="21"/>
